--- a/Data/voo.xlsx
+++ b/Data/voo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2807,7 +2807,122 @@
         <v>695</v>
       </c>
       <c r="G103" t="n">
-        <v>5064300</v>
+        <v>5080400</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C104" t="n">
+        <v>697.2999877929688</v>
+      </c>
+      <c r="D104" t="n">
+        <v>699.0599975585938</v>
+      </c>
+      <c r="E104" t="n">
+        <v>693.9400024414062</v>
+      </c>
+      <c r="F104" t="n">
+        <v>694.5399780273438</v>
+      </c>
+      <c r="G104" t="n">
+        <v>10051200</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C105" t="n">
+        <v>698.260009765625</v>
+      </c>
+      <c r="D105" t="n">
+        <v>699.1500244140625</v>
+      </c>
+      <c r="E105" t="n">
+        <v>695.780029296875</v>
+      </c>
+      <c r="F105" t="n">
+        <v>696.0599975585938</v>
+      </c>
+      <c r="G105" t="n">
+        <v>4750700</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C106" t="n">
+        <v>693.3599853515625</v>
+      </c>
+      <c r="D106" t="n">
+        <v>697.6500244140625</v>
+      </c>
+      <c r="E106" t="n">
+        <v>692.8499755859375</v>
+      </c>
+      <c r="F106" t="n">
+        <v>697.0800170898438</v>
+      </c>
+      <c r="G106" t="n">
+        <v>5970400</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="C107" t="n">
+        <v>696.0599975585938</v>
+      </c>
+      <c r="D107" t="n">
+        <v>697.2000122070312</v>
+      </c>
+      <c r="E107" t="n">
+        <v>690.9000244140625</v>
+      </c>
+      <c r="F107" t="n">
+        <v>691.489990234375</v>
+      </c>
+      <c r="G107" t="n">
+        <v>6630000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C108" t="n">
+        <v>678</v>
+      </c>
+      <c r="D108" t="n">
+        <v>692.1799926757812</v>
+      </c>
+      <c r="E108" t="n">
+        <v>676.260009765625</v>
+      </c>
+      <c r="F108" t="n">
+        <v>691.7100219726562</v>
+      </c>
+      <c r="G108" t="n">
+        <v>10731391</v>
       </c>
     </row>
   </sheetData>

--- a/Data/voo.xlsx
+++ b/Data/voo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2916,13 +2916,59 @@
         <v>692.1799926757812</v>
       </c>
       <c r="E108" t="n">
-        <v>676.260009765625</v>
+        <v>676.25</v>
       </c>
       <c r="F108" t="n">
         <v>691.7100219726562</v>
       </c>
       <c r="G108" t="n">
-        <v>10731391</v>
+        <v>10846500</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="C109" t="n">
+        <v>679.6799926757812</v>
+      </c>
+      <c r="D109" t="n">
+        <v>685.2899780273438</v>
+      </c>
+      <c r="E109" t="n">
+        <v>678.7000122070312</v>
+      </c>
+      <c r="F109" t="n">
+        <v>683.469970703125</v>
+      </c>
+      <c r="G109" t="n">
+        <v>8867200</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="C110" t="n">
+        <v>677.489990234375</v>
+      </c>
+      <c r="D110" t="n">
+        <v>686.6950073242188</v>
+      </c>
+      <c r="E110" t="n">
+        <v>664.3201293945312</v>
+      </c>
+      <c r="F110" t="n">
+        <v>683.7100219726562</v>
+      </c>
+      <c r="G110" t="n">
+        <v>9906324</v>
       </c>
     </row>
   </sheetData>

--- a/Data/voo.xlsx
+++ b/Data/voo.xlsx
@@ -2956,7 +2956,7 @@
         <v>46182</v>
       </c>
       <c r="C110" t="n">
-        <v>677.489990234375</v>
+        <v>677.6699829101562</v>
       </c>
       <c r="D110" t="n">
         <v>686.6950073242188</v>
@@ -2968,7 +2968,7 @@
         <v>683.7100219726562</v>
       </c>
       <c r="G110" t="n">
-        <v>9906324</v>
+        <v>9981615</v>
       </c>
     </row>
   </sheetData>

--- a/Data/voo.xlsx
+++ b/Data/voo.xlsx
@@ -2956,7 +2956,7 @@
         <v>46182</v>
       </c>
       <c r="C110" t="n">
-        <v>677.6699829101562</v>
+        <v>677.7000122070312</v>
       </c>
       <c r="D110" t="n">
         <v>686.6950073242188</v>
@@ -2968,7 +2968,7 @@
         <v>683.7100219726562</v>
       </c>
       <c r="G110" t="n">
-        <v>9981615</v>
+        <v>13780673</v>
       </c>
     </row>
   </sheetData>

--- a/Data/voo.xlsx
+++ b/Data/voo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2959,16 +2959,85 @@
         <v>677.7000122070312</v>
       </c>
       <c r="D110" t="n">
-        <v>686.6950073242188</v>
+        <v>686.760009765625</v>
       </c>
       <c r="E110" t="n">
-        <v>664.3201293945312</v>
+        <v>664.3200073242188</v>
       </c>
       <c r="F110" t="n">
         <v>683.7100219726562</v>
       </c>
       <c r="G110" t="n">
-        <v>13780673</v>
+        <v>16197200</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="C111" t="n">
+        <v>667.0499877929688</v>
+      </c>
+      <c r="D111" t="n">
+        <v>678.8800048828125</v>
+      </c>
+      <c r="E111" t="n">
+        <v>666.8800048828125</v>
+      </c>
+      <c r="F111" t="n">
+        <v>674.3200073242188</v>
+      </c>
+      <c r="G111" t="n">
+        <v>16472700</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C112" t="n">
+        <v>678.22998046875</v>
+      </c>
+      <c r="D112" t="n">
+        <v>680.3800048828125</v>
+      </c>
+      <c r="E112" t="n">
+        <v>666</v>
+      </c>
+      <c r="F112" t="n">
+        <v>670.0999755859375</v>
+      </c>
+      <c r="G112" t="n">
+        <v>19974200</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C113" t="n">
+        <v>681.9500122070312</v>
+      </c>
+      <c r="D113" t="n">
+        <v>684.4400024414062</v>
+      </c>
+      <c r="E113" t="n">
+        <v>675.8099975585938</v>
+      </c>
+      <c r="F113" t="n">
+        <v>681.0800170898438</v>
+      </c>
+      <c r="G113" t="n">
+        <v>6314100</v>
       </c>
     </row>
   </sheetData>

--- a/Data/voo.xlsx
+++ b/Data/voo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3037,7 +3037,122 @@
         <v>681.0800170898438</v>
       </c>
       <c r="G113" t="n">
-        <v>6314100</v>
+        <v>6328000</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="C114" t="n">
+        <v>693.8300170898438</v>
+      </c>
+      <c r="D114" t="n">
+        <v>695.75</v>
+      </c>
+      <c r="E114" t="n">
+        <v>691.260009765625</v>
+      </c>
+      <c r="F114" t="n">
+        <v>691.2999877929688</v>
+      </c>
+      <c r="G114" t="n">
+        <v>14068900</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C115" t="n">
+        <v>689.75</v>
+      </c>
+      <c r="D115" t="n">
+        <v>694.5700073242188</v>
+      </c>
+      <c r="E115" t="n">
+        <v>689.4400024414062</v>
+      </c>
+      <c r="F115" t="n">
+        <v>693.8300170898438</v>
+      </c>
+      <c r="G115" t="n">
+        <v>13324100</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C116" t="n">
+        <v>681.4099731445312</v>
+      </c>
+      <c r="D116" t="n">
+        <v>691.530029296875</v>
+      </c>
+      <c r="E116" t="n">
+        <v>679.6400146484375</v>
+      </c>
+      <c r="F116" t="n">
+        <v>690.760009765625</v>
+      </c>
+      <c r="G116" t="n">
+        <v>15029600</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C117" t="n">
+        <v>688.1099853515625</v>
+      </c>
+      <c r="D117" t="n">
+        <v>689.7000122070312</v>
+      </c>
+      <c r="E117" t="n">
+        <v>685.7000122070312</v>
+      </c>
+      <c r="F117" t="n">
+        <v>689.2999877929688</v>
+      </c>
+      <c r="G117" t="n">
+        <v>17747900</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="C118" t="n">
+        <v>686.0999755859375</v>
+      </c>
+      <c r="D118" t="n">
+        <v>691.5</v>
+      </c>
+      <c r="E118" t="n">
+        <v>685</v>
+      </c>
+      <c r="F118" t="n">
+        <v>689.1699829101562</v>
+      </c>
+      <c r="G118" t="n">
+        <v>5565075</v>
       </c>
     </row>
   </sheetData>

--- a/Data/voo.xlsx
+++ b/Data/voo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>46024</v>
       </c>
       <c r="C2" t="n">
-        <v>626.3229370117188</v>
+        <v>624.5043334960938</v>
       </c>
       <c r="D2" t="n">
-        <v>629.6723496085568</v>
+        <v>627.8440206730822</v>
       </c>
       <c r="E2" t="n">
-        <v>623.2426942846066</v>
+        <v>621.433034621939</v>
       </c>
       <c r="F2" t="n">
-        <v>628.6556005821125</v>
+        <v>626.8302238989741</v>
       </c>
       <c r="G2" t="n">
         <v>11337000</v>
@@ -495,16 +495,16 @@
         <v>46027</v>
       </c>
       <c r="C3" t="n">
-        <v>630.4699096679688</v>
+        <v>628.6392822265625</v>
       </c>
       <c r="D3" t="n">
-        <v>632.0448941989613</v>
+        <v>630.2096936449323</v>
       </c>
       <c r="E3" t="n">
-        <v>629.2437386391077</v>
+        <v>627.4166714981994</v>
       </c>
       <c r="F3" t="n">
-        <v>629.3932909831231</v>
+        <v>627.5657896032119</v>
       </c>
       <c r="G3" t="n">
         <v>16175600</v>
@@ -518,16 +518,16 @@
         <v>46028</v>
       </c>
       <c r="C4" t="n">
-        <v>634.2080688476562</v>
+        <v>632.3665771484375</v>
       </c>
       <c r="D4" t="n">
-        <v>634.6765607005819</v>
+        <v>632.8337086846144</v>
       </c>
       <c r="E4" t="n">
-        <v>630.5396559530523</v>
+        <v>628.7088158873062</v>
       </c>
       <c r="F4" t="n">
-        <v>630.6492952152564</v>
+        <v>628.8181368000583</v>
       </c>
       <c r="G4" t="n">
         <v>8672000</v>
@@ -541,16 +541,16 @@
         <v>46029</v>
       </c>
       <c r="C5" t="n">
-        <v>632.1744995117188</v>
+        <v>630.3388671875</v>
       </c>
       <c r="D5" t="n">
-        <v>636.2117435867215</v>
+        <v>634.364388398435</v>
       </c>
       <c r="E5" t="n">
-        <v>631.9352644321782</v>
+        <v>630.1003267700273</v>
       </c>
       <c r="F5" t="n">
-        <v>634.5769502621604</v>
+        <v>632.7343419902274</v>
       </c>
       <c r="G5" t="n">
         <v>8820100</v>
@@ -564,16 +564,16 @@
         <v>46030</v>
       </c>
       <c r="C6" t="n">
-        <v>632.0648193359375</v>
+        <v>630.2295532226562</v>
       </c>
       <c r="D6" t="n">
-        <v>633.1015248945556</v>
+        <v>631.2632485985795</v>
       </c>
       <c r="E6" t="n">
-        <v>630.2505389760319</v>
+        <v>628.4205408149647</v>
       </c>
       <c r="F6" t="n">
-        <v>631.4866273690646</v>
+        <v>629.6530400964517</v>
       </c>
       <c r="G6" t="n">
         <v>9017400</v>
@@ -587,16 +587,16 @@
         <v>46031</v>
       </c>
       <c r="C7" t="n">
-        <v>636.3014526367188</v>
+        <v>634.453857421875</v>
       </c>
       <c r="D7" t="n">
-        <v>637.4279017776852</v>
+        <v>635.5770357514454</v>
       </c>
       <c r="E7" t="n">
-        <v>631.8056343411428</v>
+        <v>629.9710933985081</v>
       </c>
       <c r="F7" t="n">
-        <v>633.1514228551882</v>
+        <v>631.3129742169032</v>
       </c>
       <c r="G7" t="n">
         <v>7864100</v>
@@ -610,16 +610,16 @@
         <v>46034</v>
       </c>
       <c r="C8" t="n">
-        <v>637.3282470703125</v>
+        <v>635.4776611328125</v>
       </c>
       <c r="D8" t="n">
-        <v>638.1456132747566</v>
+        <v>636.2926539819083</v>
       </c>
       <c r="E8" t="n">
-        <v>633.1613465285859</v>
+        <v>631.3228598626637</v>
       </c>
       <c r="F8" t="n">
-        <v>633.1912813337509</v>
+        <v>631.3527077472665</v>
       </c>
       <c r="G8" t="n">
         <v>7929800</v>
@@ -633,16 +633,16 @@
         <v>46035</v>
       </c>
       <c r="C9" t="n">
-        <v>636.0223999023438</v>
+        <v>634.1755981445312</v>
       </c>
       <c r="D9" t="n">
-        <v>638.1357242292579</v>
+        <v>636.2827860663717</v>
       </c>
       <c r="E9" t="n">
-        <v>633.8193319990434</v>
+        <v>631.9789272324014</v>
       </c>
       <c r="F9" t="n">
-        <v>637.667171495868</v>
+        <v>635.8155938574095</v>
       </c>
       <c r="G9" t="n">
         <v>8860000</v>
@@ -656,16 +656,16 @@
         <v>46036</v>
       </c>
       <c r="C10" t="n">
-        <v>632.9420776367188</v>
+        <v>631.104248046875</v>
       </c>
       <c r="D10" t="n">
-        <v>634.1183573055588</v>
+        <v>632.2771122348082</v>
       </c>
       <c r="E10" t="n">
-        <v>629.0144729471913</v>
+        <v>627.1880476680589</v>
       </c>
       <c r="F10" t="n">
-        <v>633.4903348185279</v>
+        <v>631.6509132926965</v>
       </c>
       <c r="G10" t="n">
         <v>8683400</v>
@@ -679,16 +679,16 @@
         <v>46037</v>
       </c>
       <c r="C11" t="n">
-        <v>634.6167602539062</v>
+        <v>632.7740478515625</v>
       </c>
       <c r="D11" t="n">
-        <v>637.5674680057444</v>
+        <v>635.7161877462142</v>
       </c>
       <c r="E11" t="n">
-        <v>633.6996722290087</v>
+        <v>631.8596227400693</v>
       </c>
       <c r="F11" t="n">
-        <v>636.7600192444881</v>
+        <v>634.911083543028</v>
       </c>
       <c r="G11" t="n">
         <v>6937000</v>
@@ -702,16 +702,16 @@
         <v>46038</v>
       </c>
       <c r="C12" t="n">
-        <v>634.0885009765625</v>
+        <v>632.247314453125</v>
       </c>
       <c r="D12" t="n">
-        <v>636.5008691494698</v>
+        <v>634.6526778944173</v>
       </c>
       <c r="E12" t="n">
-        <v>632.6829036215094</v>
+        <v>630.8457984950747</v>
       </c>
       <c r="F12" t="n">
-        <v>635.9526119524139</v>
+        <v>634.1060126577282</v>
       </c>
       <c r="G12" t="n">
         <v>6733700</v>
@@ -725,16 +725,16 @@
         <v>46042</v>
       </c>
       <c r="C13" t="n">
-        <v>621.189208984375</v>
+        <v>619.385498046875</v>
       </c>
       <c r="D13" t="n">
-        <v>627.7783952333785</v>
+        <v>625.9555516594215</v>
       </c>
       <c r="E13" t="n">
-        <v>620.262081797702</v>
+        <v>618.4610629054321</v>
       </c>
       <c r="F13" t="n">
-        <v>624.7878350890451</v>
+        <v>622.9736750304544</v>
       </c>
       <c r="G13" t="n">
         <v>14877600</v>
@@ -748,16 +748,16 @@
         <v>46043</v>
       </c>
       <c r="C14" t="n">
-        <v>628.3067016601562</v>
+        <v>626.4822998046875</v>
       </c>
       <c r="D14" t="n">
-        <v>631.4069619456919</v>
+        <v>629.5735579251939</v>
       </c>
       <c r="E14" t="n">
-        <v>621.6876413873049</v>
+        <v>619.8824591674239</v>
       </c>
       <c r="F14" t="n">
-        <v>623.0533256649838</v>
+        <v>621.2441779344317</v>
       </c>
       <c r="G14" t="n">
         <v>10403800</v>
@@ -771,16 +771,16 @@
         <v>46044</v>
       </c>
       <c r="C15" t="n">
-        <v>631.5763549804688</v>
+        <v>629.7424926757812</v>
       </c>
       <c r="D15" t="n">
-        <v>633.6198920846093</v>
+        <v>631.7800961099325</v>
       </c>
       <c r="E15" t="n">
-        <v>629.7620746664077</v>
+        <v>627.9334803554502</v>
       </c>
       <c r="F15" t="n">
-        <v>632.4336342193808</v>
+        <v>630.5972826953481</v>
       </c>
       <c r="G15" t="n">
         <v>6085500</v>
@@ -794,16 +794,16 @@
         <v>46045</v>
       </c>
       <c r="C16" t="n">
-        <v>631.8355712890625</v>
+        <v>630.0009765625</v>
       </c>
       <c r="D16" t="n">
-        <v>633.4703645304628</v>
+        <v>631.6310230261056</v>
       </c>
       <c r="E16" t="n">
-        <v>629.9813778307397</v>
+        <v>628.1521669313868</v>
       </c>
       <c r="F16" t="n">
-        <v>630.8885484448035</v>
+        <v>629.0567034892177</v>
       </c>
       <c r="G16" t="n">
         <v>5850400</v>
@@ -817,16 +817,16 @@
         <v>46048</v>
       </c>
       <c r="C17" t="n">
-        <v>635.0853271484375</v>
+        <v>633.2412719726562</v>
       </c>
       <c r="D17" t="n">
-        <v>636.3812243340543</v>
+        <v>634.5334063474975</v>
       </c>
       <c r="E17" t="n">
-        <v>632.5234067392744</v>
+        <v>630.6867904420004</v>
       </c>
       <c r="F17" t="n">
-        <v>633.0318116823709</v>
+        <v>631.1937191633569</v>
       </c>
       <c r="G17" t="n">
         <v>9007400</v>
@@ -840,16 +840,16 @@
         <v>46049</v>
       </c>
       <c r="C18" t="n">
-        <v>637.6870727539062</v>
+        <v>635.83544921875</v>
       </c>
       <c r="D18" t="n">
-        <v>638.5842042244849</v>
+        <v>636.7299757286575</v>
       </c>
       <c r="E18" t="n">
-        <v>635.8628141657504</v>
+        <v>634.01648764896</v>
       </c>
       <c r="F18" t="n">
-        <v>636.4110713160646</v>
+        <v>634.5631528494195</v>
       </c>
       <c r="G18" t="n">
         <v>4339600</v>
@@ -863,16 +863,16 @@
         <v>46050</v>
       </c>
       <c r="C19" t="n">
-        <v>637.58740234375</v>
+        <v>635.736083984375</v>
       </c>
       <c r="D19" t="n">
-        <v>639.7904702337662</v>
+        <v>637.9327549788177</v>
       </c>
       <c r="E19" t="n">
-        <v>636.2117398014742</v>
+        <v>634.3644158580984</v>
       </c>
       <c r="F19" t="n">
-        <v>639.032851924327</v>
+        <v>637.1773365131655</v>
       </c>
       <c r="G19" t="n">
         <v>5568700</v>
@@ -886,16 +886,16 @@
         <v>46051</v>
       </c>
       <c r="C20" t="n">
-        <v>636.2615966796875</v>
+        <v>634.4141235351562</v>
       </c>
       <c r="D20" t="n">
-        <v>639.0228390403352</v>
+        <v>637.1673482484503</v>
       </c>
       <c r="E20" t="n">
-        <v>627.8381738425048</v>
+        <v>626.0151592658927</v>
       </c>
       <c r="F20" t="n">
-        <v>638.4147731092087</v>
+        <v>636.5610479204715</v>
       </c>
       <c r="G20" t="n">
         <v>8697200</v>
@@ -909,16 +909,16 @@
         <v>46052</v>
       </c>
       <c r="C21" t="n">
-        <v>634.218017578125</v>
+        <v>632.37646484375</v>
       </c>
       <c r="D21" t="n">
-        <v>636.4410419515368</v>
+        <v>634.5930343128545</v>
       </c>
       <c r="E21" t="n">
-        <v>629.9614950902494</v>
+        <v>628.1323018448974</v>
       </c>
       <c r="F21" t="n">
-        <v>634.2479523837117</v>
+        <v>632.4063127288746</v>
       </c>
       <c r="G21" t="n">
         <v>6562300</v>
@@ -932,16 +932,16 @@
         <v>46055</v>
       </c>
       <c r="C22" t="n">
-        <v>637.6671142578125</v>
+        <v>635.8155517578125</v>
       </c>
       <c r="D22" t="n">
-        <v>638.9431156917317</v>
+        <v>637.0878481294003</v>
       </c>
       <c r="E22" t="n">
-        <v>632.0747818242223</v>
+        <v>630.2394575036581</v>
       </c>
       <c r="F22" t="n">
-        <v>632.1844210853287</v>
+        <v>630.3487784106579</v>
       </c>
       <c r="G22" t="n">
         <v>9490300</v>
@@ -955,16 +955,16 @@
         <v>46056</v>
       </c>
       <c r="C23" t="n">
-        <v>632.1546020507812</v>
+        <v>630.3190307617188</v>
       </c>
       <c r="D23" t="n">
-        <v>638.9830234398476</v>
+        <v>637.127624636739</v>
       </c>
       <c r="E23" t="n">
-        <v>627.1304220220587</v>
+        <v>625.3094393171525</v>
       </c>
       <c r="F23" t="n">
-        <v>638.3151487041461</v>
+        <v>636.4616891919731</v>
       </c>
       <c r="G23" t="n">
         <v>9702800</v>
@@ -978,16 +978,16 @@
         <v>46057</v>
       </c>
       <c r="C24" t="n">
-        <v>628.9247436523438</v>
+        <v>627.0985717773438</v>
       </c>
       <c r="D24" t="n">
-        <v>633.9189888563574</v>
+        <v>632.0783154846036</v>
       </c>
       <c r="E24" t="n">
-        <v>625.0270736799457</v>
+        <v>623.2122192405427</v>
       </c>
       <c r="F24" t="n">
-        <v>632.9321137380748</v>
+        <v>631.0943058976957</v>
       </c>
       <c r="G24" t="n">
         <v>11322000</v>
@@ -1001,16 +1001,16 @@
         <v>46058</v>
       </c>
       <c r="C25" t="n">
-        <v>621.1392822265625</v>
+        <v>619.335693359375</v>
       </c>
       <c r="D25" t="n">
-        <v>626.7715278478421</v>
+        <v>624.9515847493406</v>
       </c>
       <c r="E25" t="n">
-        <v>619.5443412444276</v>
+        <v>617.7453835733044</v>
       </c>
       <c r="F25" t="n">
-        <v>624.269416268178</v>
+        <v>622.456738497629</v>
       </c>
       <c r="G25" t="n">
         <v>11714700</v>
@@ -1024,16 +1024,16 @@
         <v>46059</v>
       </c>
       <c r="C26" t="n">
-        <v>633.2410888671875</v>
+        <v>631.4024047851562</v>
       </c>
       <c r="D26" t="n">
-        <v>634.7164123007573</v>
+        <v>632.873444457358</v>
       </c>
       <c r="E26" t="n">
-        <v>624.2295568204432</v>
+        <v>622.4170386976657</v>
       </c>
       <c r="F26" t="n">
-        <v>624.7478791699393</v>
+        <v>622.9338560420853</v>
       </c>
       <c r="G26" t="n">
         <v>12987900</v>
@@ -1047,16 +1047,16 @@
         <v>46062</v>
       </c>
       <c r="C27" t="n">
-        <v>636.2216796875</v>
+        <v>634.3743286132812</v>
       </c>
       <c r="D27" t="n">
-        <v>637.9761512786496</v>
+        <v>636.1237058716187</v>
       </c>
       <c r="E27" t="n">
-        <v>631.1177955185733</v>
+        <v>629.2852642252629</v>
       </c>
       <c r="F27" t="n">
-        <v>632.0747966164091</v>
+        <v>630.2394865479288</v>
       </c>
       <c r="G27" t="n">
         <v>8908500</v>
@@ -1070,16 +1070,16 @@
         <v>46063</v>
       </c>
       <c r="C28" t="n">
-        <v>634.4373779296875</v>
+        <v>632.59521484375</v>
       </c>
       <c r="D28" t="n">
-        <v>638.6042178247523</v>
+        <v>636.7499558321192</v>
       </c>
       <c r="E28" t="n">
-        <v>634.0785253093898</v>
+        <v>632.2374041939814</v>
       </c>
       <c r="F28" t="n">
-        <v>637.1288942681263</v>
+        <v>635.2789160498899</v>
       </c>
       <c r="G28" t="n">
         <v>13645300</v>
@@ -1093,16 +1093,16 @@
         <v>46064</v>
       </c>
       <c r="C29" t="n">
-        <v>634.3475952148438</v>
+        <v>632.5056762695312</v>
       </c>
       <c r="D29" t="n">
-        <v>639.1325398960017</v>
+        <v>637.276727179629</v>
       </c>
       <c r="E29" t="n">
-        <v>631.8455444528879</v>
+        <v>630.0108905697201</v>
       </c>
       <c r="F29" t="n">
-        <v>638.4745826229479</v>
+        <v>636.620680379596</v>
       </c>
       <c r="G29" t="n">
         <v>5345000</v>
@@ -1116,16 +1116,16 @@
         <v>46065</v>
       </c>
       <c r="C30" t="n">
-        <v>624.5186767578125</v>
+        <v>622.705322265625</v>
       </c>
       <c r="D30" t="n">
-        <v>637.5077057629776</v>
+        <v>635.656636283277</v>
       </c>
       <c r="E30" t="n">
-        <v>623.7909932456909</v>
+        <v>621.9797516577522</v>
       </c>
       <c r="F30" t="n">
-        <v>636.5008740941993</v>
+        <v>634.652728054257</v>
       </c>
       <c r="G30" t="n">
         <v>8951100</v>
@@ -1139,16 +1139,16 @@
         <v>46066</v>
       </c>
       <c r="C31" t="n">
-        <v>624.9174194335938</v>
+        <v>623.1029052734375</v>
       </c>
       <c r="D31" t="n">
-        <v>629.1839201895053</v>
+        <v>627.3570177908472</v>
       </c>
       <c r="E31" t="n">
-        <v>621.1592627846891</v>
+        <v>619.3556608318796</v>
       </c>
       <c r="F31" t="n">
-        <v>624.9572716646039</v>
+        <v>623.1426417892584</v>
       </c>
       <c r="G31" t="n">
         <v>9312800</v>
@@ -1162,16 +1162,16 @@
         <v>46070</v>
       </c>
       <c r="C32" t="n">
-        <v>626.013916015625</v>
+        <v>624.1961669921875</v>
       </c>
       <c r="D32" t="n">
-        <v>627.947813918952</v>
+        <v>626.1244494596028</v>
       </c>
       <c r="E32" t="n">
-        <v>619.5543258756086</v>
+        <v>617.7553334857993</v>
       </c>
       <c r="F32" t="n">
-        <v>623.5716131766302</v>
+        <v>621.7609558383565</v>
       </c>
       <c r="G32" t="n">
         <v>8718600</v>
@@ -1185,16 +1185,16 @@
         <v>46071</v>
       </c>
       <c r="C33" t="n">
-        <v>629.1640014648438</v>
+        <v>627.337158203125</v>
       </c>
       <c r="D33" t="n">
-        <v>631.8056262746594</v>
+        <v>629.9711127799449</v>
       </c>
       <c r="E33" t="n">
-        <v>626.0238891485947</v>
+        <v>624.2061635303085</v>
       </c>
       <c r="F33" t="n">
-        <v>627.1303817388545</v>
+        <v>625.3094433039927</v>
       </c>
       <c r="G33" t="n">
         <v>9509200</v>
@@ -1208,16 +1208,16 @@
         <v>46072</v>
       </c>
       <c r="C34" t="n">
-        <v>627.5491333007812</v>
+        <v>625.7269287109375</v>
       </c>
       <c r="D34" t="n">
-        <v>629.0942438607823</v>
+        <v>627.2675527576046</v>
       </c>
       <c r="E34" t="n">
-        <v>624.8376604869816</v>
+        <v>623.0233291582808</v>
       </c>
       <c r="F34" t="n">
-        <v>626.9709413081965</v>
+        <v>625.1504156053861</v>
       </c>
       <c r="G34" t="n">
         <v>5212400</v>
@@ -1231,16 +1231,16 @@
         <v>46073</v>
       </c>
       <c r="C35" t="n">
-        <v>632.0249633789062</v>
+        <v>630.1898193359375</v>
       </c>
       <c r="D35" t="n">
-        <v>632.5831988061159</v>
+        <v>630.7464338739763</v>
       </c>
       <c r="E35" t="n">
-        <v>625.0569683853632</v>
+        <v>623.2420565725196</v>
       </c>
       <c r="F35" t="n">
-        <v>625.5055037062776</v>
+        <v>623.6892895288598</v>
       </c>
       <c r="G35" t="n">
         <v>7482000</v>
@@ -1254,16 +1254,16 @@
         <v>46076</v>
       </c>
       <c r="C36" t="n">
-        <v>625.6550903320312</v>
+        <v>623.8384399414062</v>
       </c>
       <c r="D36" t="n">
-        <v>632.613107438793</v>
+        <v>630.7762537689327</v>
       </c>
       <c r="E36" t="n">
-        <v>623.781001114451</v>
+        <v>621.9697923240972</v>
       </c>
       <c r="F36" t="n">
-        <v>630.6194006833334</v>
+        <v>628.7883359348965</v>
       </c>
       <c r="G36" t="n">
         <v>10868700</v>
@@ -1277,16 +1277,16 @@
         <v>46077</v>
       </c>
       <c r="C37" t="n">
-        <v>630.220703125</v>
+        <v>628.3907470703125</v>
       </c>
       <c r="D37" t="n">
-        <v>631.0979389749934</v>
+        <v>629.2654357125624</v>
       </c>
       <c r="E37" t="n">
-        <v>623.4321339778913</v>
+        <v>621.6218897212324</v>
       </c>
       <c r="F37" t="n">
-        <v>625.1766274090892</v>
+        <v>623.3613177105922</v>
       </c>
       <c r="G37" t="n">
         <v>6930300</v>
@@ -1300,16 +1300,16 @@
         <v>46078</v>
       </c>
       <c r="C38" t="n">
-        <v>635.52392578125</v>
+        <v>633.6785888671875</v>
       </c>
       <c r="D38" t="n">
-        <v>635.9924176365773</v>
+        <v>634.1457203877115</v>
       </c>
       <c r="E38" t="n">
-        <v>632.7426660811561</v>
+        <v>630.9054049624871</v>
       </c>
       <c r="F38" t="n">
-        <v>632.7726008854187</v>
+        <v>630.9352528466555</v>
       </c>
       <c r="G38" t="n">
         <v>12135200</v>
@@ -1323,16 +1323,16 @@
         <v>46079</v>
       </c>
       <c r="C39" t="n">
-        <v>631.9552001953125</v>
+        <v>630.1202392578125</v>
       </c>
       <c r="D39" t="n">
-        <v>635.7631873344244</v>
+        <v>633.9171694301511</v>
       </c>
       <c r="E39" t="n">
-        <v>627.4494035350784</v>
+        <v>625.6275257415438</v>
       </c>
       <c r="F39" t="n">
-        <v>635.6435697985864</v>
+        <v>633.7978992187842</v>
       </c>
       <c r="G39" t="n">
         <v>9497700</v>
@@ -1346,16 +1346,16 @@
         <v>46080</v>
       </c>
       <c r="C40" t="n">
-        <v>629.0543212890625</v>
+        <v>627.227783203125</v>
       </c>
       <c r="D40" t="n">
-        <v>629.7023003091678</v>
+        <v>627.8738807349088</v>
       </c>
       <c r="E40" t="n">
-        <v>624.9672468574614</v>
+        <v>623.1525761045295</v>
       </c>
       <c r="F40" t="n">
-        <v>626.2631440545715</v>
+        <v>624.4447105016621</v>
       </c>
       <c r="G40" t="n">
         <v>10471100</v>
@@ -1369,16 +1369,16 @@
         <v>46083</v>
       </c>
       <c r="C41" t="n">
-        <v>629.2936401367188</v>
+        <v>627.4663696289062</v>
       </c>
       <c r="D41" t="n">
-        <v>631.3471556958345</v>
+        <v>629.5139224256816</v>
       </c>
       <c r="E41" t="n">
-        <v>621.637752524395</v>
+        <v>619.8327123026569</v>
       </c>
       <c r="F41" t="n">
-        <v>622.2259227981638</v>
+        <v>620.4191747152204</v>
       </c>
       <c r="G41" t="n">
         <v>9211400</v>
@@ -1392,16 +1392,16 @@
         <v>46084</v>
       </c>
       <c r="C42" t="n">
-        <v>623.7510375976562</v>
+        <v>621.9398803710938</v>
       </c>
       <c r="D42" t="n">
-        <v>625.8145312957482</v>
+        <v>623.9973823973519</v>
       </c>
       <c r="E42" t="n">
-        <v>613.9420348844322</v>
+        <v>612.1593596083252</v>
       </c>
       <c r="F42" t="n">
-        <v>618.8565145092585</v>
+        <v>617.0595692844848</v>
       </c>
       <c r="G42" t="n">
         <v>18493400</v>
@@ -1415,16 +1415,16 @@
         <v>46085</v>
       </c>
       <c r="C43" t="n">
-        <v>628.197021484375</v>
+        <v>626.3729858398438</v>
       </c>
       <c r="D43" t="n">
-        <v>629.9714496087968</v>
+        <v>628.1422617269309</v>
       </c>
       <c r="E43" t="n">
-        <v>623.1031155924247</v>
+        <v>621.2938706355266</v>
       </c>
       <c r="F43" t="n">
-        <v>624.9472699077184</v>
+        <v>623.13267025621</v>
       </c>
       <c r="G43" t="n">
         <v>13489800</v>
@@ -1438,16 +1438,16 @@
         <v>46086</v>
       </c>
       <c r="C44" t="n">
-        <v>624.837646484375</v>
+        <v>623.0233154296875</v>
       </c>
       <c r="D44" t="n">
-        <v>628.5160377831583</v>
+        <v>626.6910258426402</v>
       </c>
       <c r="E44" t="n">
-        <v>619.4446966266207</v>
+        <v>617.646024993958</v>
       </c>
       <c r="F44" t="n">
-        <v>625.316116623046</v>
+        <v>623.5003962422892</v>
       </c>
       <c r="G44" t="n">
         <v>12198800</v>
@@ -1461,16 +1461,16 @@
         <v>46087</v>
       </c>
       <c r="C45" t="n">
-        <v>616.4840087890625</v>
+        <v>614.6939697265625</v>
       </c>
       <c r="D45" t="n">
-        <v>619.8633562416012</v>
+        <v>618.0635048176132</v>
       </c>
       <c r="E45" t="n">
-        <v>614.0616624542542</v>
+        <v>612.2786569798124</v>
       </c>
       <c r="F45" t="n">
-        <v>617.3911794080059</v>
+        <v>615.5985062612132</v>
       </c>
       <c r="G45" t="n">
         <v>9739200</v>
@@ -1484,16 +1484,16 @@
         <v>46090</v>
       </c>
       <c r="C46" t="n">
-        <v>621.8370971679688</v>
+        <v>620.031494140625</v>
       </c>
       <c r="D46" t="n">
-        <v>623.352333704435</v>
+        <v>621.542330946535</v>
       </c>
       <c r="E46" t="n">
-        <v>607.2830628384654</v>
+        <v>605.5197197672502</v>
       </c>
       <c r="F46" t="n">
-        <v>610.931519267521</v>
+        <v>609.1575823221168</v>
       </c>
       <c r="G46" t="n">
         <v>13929200</v>
@@ -1507,16 +1507,16 @@
         <v>46091</v>
       </c>
       <c r="C47" t="n">
-        <v>620.760498046875</v>
+        <v>618.9580078125</v>
       </c>
       <c r="D47" t="n">
-        <v>626.5223396993956</v>
+        <v>624.7031189170179</v>
       </c>
       <c r="E47" t="n">
-        <v>618.6771085868369</v>
+        <v>616.8806678500829</v>
       </c>
       <c r="F47" t="n">
-        <v>621.3586465715416</v>
+        <v>619.5544195048814</v>
       </c>
       <c r="G47" t="n">
         <v>15570400</v>
@@ -1530,16 +1530,16 @@
         <v>46092</v>
       </c>
       <c r="C48" t="n">
-        <v>620.0726928710938</v>
+        <v>618.272216796875</v>
       </c>
       <c r="D48" t="n">
-        <v>623.46195761512</v>
+        <v>621.6516402913978</v>
       </c>
       <c r="E48" t="n">
-        <v>617.3512419647918</v>
+        <v>615.5586680402731</v>
       </c>
       <c r="F48" t="n">
-        <v>621.2389942063103</v>
+        <v>619.4351315974586</v>
       </c>
       <c r="G48" t="n">
         <v>6433300</v>
@@ -1553,16 +1553,16 @@
         <v>46093</v>
       </c>
       <c r="C49" t="n">
-        <v>610.5726928710938</v>
+        <v>608.7998046875</v>
       </c>
       <c r="D49" t="n">
-        <v>615.766320864175</v>
+        <v>613.9783522130032</v>
       </c>
       <c r="E49" t="n">
-        <v>610.4929275649361</v>
+        <v>608.7202709917146</v>
       </c>
       <c r="F49" t="n">
-        <v>615.2778116016729</v>
+        <v>613.491261409448</v>
       </c>
       <c r="G49" t="n">
         <v>15487600</v>
@@ -1576,16 +1576,16 @@
         <v>46094</v>
       </c>
       <c r="C50" t="n">
-        <v>607.1734619140625</v>
+        <v>605.4104614257812</v>
       </c>
       <c r="D50" t="n">
-        <v>616.3843775608374</v>
+        <v>614.5946320815423</v>
       </c>
       <c r="E50" t="n">
-        <v>606.336078290218</v>
+        <v>604.5755092450586</v>
       </c>
       <c r="F50" t="n">
-        <v>613.6031176456171</v>
+        <v>611.8214478858587</v>
       </c>
       <c r="G50" t="n">
         <v>25527500</v>
@@ -1599,16 +1599,16 @@
         <v>46097</v>
       </c>
       <c r="C51" t="n">
-        <v>613.2542114257812</v>
+        <v>611.4735717773438</v>
       </c>
       <c r="D51" t="n">
-        <v>616.1351321936789</v>
+        <v>614.3461275285033</v>
       </c>
       <c r="E51" t="n">
-        <v>611.6093790701457</v>
+        <v>609.8335153427746</v>
       </c>
       <c r="F51" t="n">
-        <v>612.7856587154628</v>
+        <v>611.006379552641</v>
       </c>
       <c r="G51" t="n">
         <v>8303200</v>
@@ -1622,16 +1622,16 @@
         <v>46098</v>
       </c>
       <c r="C52" t="n">
-        <v>614.9488525390625</v>
+        <v>613.1632690429688</v>
       </c>
       <c r="D52" t="n">
-        <v>618.3182215917396</v>
+        <v>616.5228546969976</v>
       </c>
       <c r="E52" t="n">
-        <v>614.3308083547819</v>
+        <v>612.5470194298802</v>
       </c>
       <c r="F52" t="n">
-        <v>616.4241759669457</v>
+        <v>614.6343086785441</v>
       </c>
       <c r="G52" t="n">
         <v>9941800</v>
@@ -1645,16 +1645,16 @@
         <v>46099</v>
       </c>
       <c r="C53" t="n">
-        <v>606.4656372070312</v>
+        <v>604.7046508789062</v>
       </c>
       <c r="D53" t="n">
-        <v>613.9520154926196</v>
+        <v>612.1692910659127</v>
       </c>
       <c r="E53" t="n">
-        <v>606.21642387312</v>
+        <v>604.4561611824888</v>
       </c>
       <c r="F53" t="n">
-        <v>612.755779321226</v>
+        <v>610.9765283898234</v>
       </c>
       <c r="G53" t="n">
         <v>14276900</v>
@@ -1668,16 +1668,16 @@
         <v>46100</v>
       </c>
       <c r="C54" t="n">
-        <v>604.8407592773438</v>
+        <v>603.0845336914062</v>
       </c>
       <c r="D54" t="n">
-        <v>607.7715105075661</v>
+        <v>606.0067751441085</v>
       </c>
       <c r="E54" t="n">
-        <v>600.6439848455091</v>
+        <v>598.8999450829019</v>
       </c>
       <c r="F54" t="n">
-        <v>602.2389866827961</v>
+        <v>600.4903156465963</v>
       </c>
       <c r="G54" t="n">
         <v>10271900</v>
@@ -1691,16 +1691,16 @@
         <v>46101</v>
       </c>
       <c r="C55" t="n">
-        <v>596.0584716796875</v>
+        <v>594.3277587890625</v>
       </c>
       <c r="D55" t="n">
-        <v>603.6943412769623</v>
+        <v>601.9414569072442</v>
       </c>
       <c r="E55" t="n">
-        <v>592.6990808864354</v>
+        <v>590.9781223088967</v>
       </c>
       <c r="F55" t="n">
-        <v>603.5248932500269</v>
+        <v>601.7725008888926</v>
       </c>
       <c r="G55" t="n">
         <v>17685700</v>
@@ -1714,16 +1714,16 @@
         <v>46104</v>
       </c>
       <c r="C56" t="n">
-        <v>602.528076171875</v>
+        <v>600.778564453125</v>
       </c>
       <c r="D56" t="n">
-        <v>609.107344931135</v>
+        <v>607.3387295253531</v>
       </c>
       <c r="E56" t="n">
-        <v>601.1623919200568</v>
+        <v>599.416845627479</v>
       </c>
       <c r="F56" t="n">
-        <v>604.9504225639998</v>
+        <v>603.1938772752512</v>
       </c>
       <c r="G56" t="n">
         <v>24014300</v>
@@ -1737,16 +1737,16 @@
         <v>46105</v>
       </c>
       <c r="C57" t="n">
-        <v>600.4844970703125</v>
+        <v>598.7409057617188</v>
       </c>
       <c r="D57" t="n">
-        <v>604.0033575888065</v>
+        <v>602.2495487731062</v>
       </c>
       <c r="E57" t="n">
-        <v>597.4341283991844</v>
+        <v>595.6993942656367</v>
       </c>
       <c r="F57" t="n">
-        <v>598.7400037913939</v>
+        <v>597.0014778647273</v>
       </c>
       <c r="G57" t="n">
         <v>18363300</v>
@@ -1760,16 +1760,16 @@
         <v>46106</v>
       </c>
       <c r="C58" t="n">
-        <v>603.754150390625</v>
+        <v>602.0010375976562</v>
       </c>
       <c r="D58" t="n">
-        <v>607.5222851160179</v>
+        <v>605.7582308410098</v>
       </c>
       <c r="E58" t="n">
-        <v>601.4613999408256</v>
+        <v>599.7149445764509</v>
       </c>
       <c r="F58" t="n">
-        <v>605.4887262623266</v>
+        <v>603.7305768047668</v>
       </c>
       <c r="G58" t="n">
         <v>23288300</v>
@@ -1783,16 +1783,16 @@
         <v>46107</v>
       </c>
       <c r="C59" t="n">
-        <v>593.0479736328125</v>
+        <v>591.3259887695312</v>
       </c>
       <c r="D59" t="n">
-        <v>602.0096754492398</v>
+        <v>600.2616692258608</v>
       </c>
       <c r="E59" t="n">
-        <v>592.8087385654484</v>
+        <v>591.0874483494522</v>
       </c>
       <c r="F59" t="n">
-        <v>599.407902827006</v>
+        <v>597.6674511578492</v>
       </c>
       <c r="G59" t="n">
         <v>7712600</v>
@@ -1806,16 +1806,16 @@
         <v>46108</v>
       </c>
       <c r="C60" t="n">
-        <v>582.9600219726562</v>
+        <v>581.267333984375</v>
       </c>
       <c r="D60" t="n">
-        <v>590.8300170898438</v>
+        <v>589.1144777126154</v>
       </c>
       <c r="E60" t="n">
-        <v>582.030029296875</v>
+        <v>580.340041643732</v>
       </c>
       <c r="F60" t="n">
-        <v>590.6799926757812</v>
+        <v>588.9648889107974</v>
       </c>
       <c r="G60" t="n">
         <v>11707700</v>
@@ -1829,16 +1829,16 @@
         <v>46111</v>
       </c>
       <c r="C61" t="n">
-        <v>580.9299926757812</v>
+        <v>579.2431640625</v>
       </c>
       <c r="D61" t="n">
-        <v>588.6699829101562</v>
+        <v>586.9606799244748</v>
       </c>
       <c r="E61" t="n">
-        <v>578.4600219726562</v>
+        <v>576.780365337597</v>
       </c>
       <c r="F61" t="n">
-        <v>588.3900146484375</v>
+        <v>586.681524598016</v>
       </c>
       <c r="G61" t="n">
         <v>11839200</v>
@@ -1852,16 +1852,16 @@
         <v>46112</v>
       </c>
       <c r="C62" t="n">
-        <v>597.5499877929688</v>
+        <v>595.81494140625</v>
       </c>
       <c r="D62" t="n">
-        <v>598.8499755859375</v>
+        <v>597.1111545541363</v>
       </c>
       <c r="E62" t="n">
-        <v>586.5</v>
+        <v>584.797038362315</v>
       </c>
       <c r="F62" t="n">
-        <v>587.3499755859375</v>
+        <v>585.6445459587967</v>
       </c>
       <c r="G62" t="n">
         <v>12447300</v>
@@ -1875,16 +1875,16 @@
         <v>46113</v>
       </c>
       <c r="C63" t="n">
-        <v>602.2999877929688</v>
+        <v>600.5511474609375</v>
       </c>
       <c r="D63" t="n">
-        <v>605.3499755859375</v>
+        <v>603.5922792987799</v>
       </c>
       <c r="E63" t="n">
-        <v>600.27001953125</v>
+        <v>598.5270734220991</v>
       </c>
       <c r="F63" t="n">
-        <v>601.0599975585938</v>
+        <v>599.3147576665046</v>
       </c>
       <c r="G63" t="n">
         <v>11332500</v>
@@ -1898,16 +1898,16 @@
         <v>46114</v>
       </c>
       <c r="C64" t="n">
-        <v>602.989990234375</v>
+        <v>601.2391357421875</v>
       </c>
       <c r="D64" t="n">
-        <v>604.7899780273438</v>
+        <v>603.033897052521</v>
       </c>
       <c r="E64" t="n">
-        <v>593.030029296875</v>
+        <v>591.3080947579734</v>
       </c>
       <c r="F64" t="n">
-        <v>594.22998046875</v>
+        <v>592.5045617262401</v>
       </c>
       <c r="G64" t="n">
         <v>12780100</v>
@@ -1921,16 +1921,16 @@
         <v>46118</v>
       </c>
       <c r="C65" t="n">
-        <v>605.6699829101562</v>
+        <v>603.9113159179688</v>
       </c>
       <c r="D65" t="n">
-        <v>606.4400024414062</v>
+        <v>604.679099565039</v>
       </c>
       <c r="E65" t="n">
-        <v>602.6099853515625</v>
+        <v>600.860203588715</v>
       </c>
       <c r="F65" t="n">
-        <v>602.9199829101562</v>
+        <v>601.1693010160667</v>
       </c>
       <c r="G65" t="n">
         <v>6316800</v>
@@ -1944,16 +1944,16 @@
         <v>46119</v>
       </c>
       <c r="C66" t="n">
-        <v>606.0399780273438</v>
+        <v>604.2802734375</v>
       </c>
       <c r="D66" t="n">
-        <v>606.3099975585938</v>
+        <v>604.5495089369605</v>
       </c>
       <c r="E66" t="n">
-        <v>598.5</v>
+        <v>596.762188576322</v>
       </c>
       <c r="F66" t="n">
-        <v>603.5800170898438</v>
+        <v>601.8274552706249</v>
       </c>
       <c r="G66" t="n">
         <v>6690000</v>
@@ -1967,16 +1967,16 @@
         <v>46120</v>
       </c>
       <c r="C67" t="n">
-        <v>621.3400268554688</v>
+        <v>619.535888671875</v>
       </c>
       <c r="D67" t="n">
-        <v>622.489990234375</v>
+        <v>620.6825129888314</v>
       </c>
       <c r="E67" t="n">
-        <v>617.2999877929688</v>
+        <v>615.50758036616</v>
       </c>
       <c r="F67" t="n">
-        <v>621.7999877929688</v>
+        <v>619.9945140554843</v>
       </c>
       <c r="G67" t="n">
         <v>9805100</v>
@@ -1990,16 +1990,16 @@
         <v>46121</v>
       </c>
       <c r="C68" t="n">
-        <v>625.02001953125</v>
+        <v>623.2052001953125</v>
       </c>
       <c r="D68" t="n">
-        <v>626.1699829101562</v>
+        <v>624.3518245199318</v>
       </c>
       <c r="E68" t="n">
-        <v>619.4000244140625</v>
+        <v>617.6015233967194</v>
       </c>
       <c r="F68" t="n">
-        <v>620.3400268554688</v>
+        <v>618.5387964301815</v>
       </c>
       <c r="G68" t="n">
         <v>5498300</v>
@@ -2013,16 +2013,16 @@
         <v>46122</v>
       </c>
       <c r="C69" t="n">
-        <v>624.5999755859375</v>
+        <v>622.786376953125</v>
       </c>
       <c r="D69" t="n">
-        <v>626.989990234375</v>
+        <v>625.1694519162147</v>
       </c>
       <c r="E69" t="n">
-        <v>623.719970703125</v>
+        <v>621.9089272667818</v>
       </c>
       <c r="F69" t="n">
-        <v>626.3300170898438</v>
+        <v>624.5113950804241</v>
       </c>
       <c r="G69" t="n">
         <v>4609400</v>
@@ -2036,16 +2036,16 @@
         <v>46125</v>
       </c>
       <c r="C70" t="n">
-        <v>630.719970703125</v>
+        <v>628.8886108398438</v>
       </c>
       <c r="D70" t="n">
-        <v>630.9000244140625</v>
+        <v>629.068141746439</v>
       </c>
       <c r="E70" t="n">
-        <v>621.97998046875</v>
+        <v>620.1739980599084</v>
       </c>
       <c r="F70" t="n">
-        <v>622.75</v>
+        <v>620.9417817607915</v>
       </c>
       <c r="G70" t="n">
         <v>5158400</v>
@@ -2059,16 +2059,16 @@
         <v>46126</v>
       </c>
       <c r="C71" t="n">
-        <v>638.3499755859375</v>
+        <v>636.4964599609375</v>
       </c>
       <c r="D71" t="n">
-        <v>638.52001953125</v>
+        <v>636.6660101659483</v>
       </c>
       <c r="E71" t="n">
-        <v>632.219970703125</v>
+        <v>630.3842541856149</v>
       </c>
       <c r="F71" t="n">
-        <v>632.22998046875</v>
+        <v>630.394234886843</v>
       </c>
       <c r="G71" t="n">
         <v>5042900</v>
@@ -2082,16 +2082,16 @@
         <v>46127</v>
       </c>
       <c r="C72" t="n">
-        <v>643.4500122070312</v>
+        <v>641.5816650390625</v>
       </c>
       <c r="D72" t="n">
-        <v>643.7899780273438</v>
+        <v>641.9206437210339</v>
       </c>
       <c r="E72" t="n">
-        <v>638.22998046875</v>
+        <v>636.3767903935311</v>
       </c>
       <c r="F72" t="n">
-        <v>639.1900024414062</v>
+        <v>637.3340248080247</v>
       </c>
       <c r="G72" t="n">
         <v>5165600</v>
@@ -2105,16 +2105,16 @@
         <v>46128</v>
       </c>
       <c r="C73" t="n">
-        <v>644.8599853515625</v>
+        <v>642.987548828125</v>
       </c>
       <c r="D73" t="n">
-        <v>646.0700073242188</v>
+        <v>644.1940573414455</v>
       </c>
       <c r="E73" t="n">
-        <v>642.1500244140625</v>
+        <v>640.2854566217476</v>
       </c>
       <c r="F73" t="n">
-        <v>644.510009765625</v>
+        <v>642.6385894427339</v>
       </c>
       <c r="G73" t="n">
         <v>5882400</v>
@@ -2128,16 +2128,16 @@
         <v>46129</v>
       </c>
       <c r="C74" t="n">
-        <v>652.780029296875</v>
+        <v>650.8845825195312</v>
       </c>
       <c r="D74" t="n">
-        <v>654.8800048828125</v>
+        <v>652.978460504779</v>
       </c>
       <c r="E74" t="n">
-        <v>648.8599853515625</v>
+        <v>646.9759210221027</v>
       </c>
       <c r="F74" t="n">
-        <v>649.1799926757812</v>
+        <v>647.2949991560519</v>
       </c>
       <c r="G74" t="n">
         <v>7815300</v>
@@ -2151,16 +2151,16 @@
         <v>46132</v>
       </c>
       <c r="C75" t="n">
-        <v>651.5399780273438</v>
+        <v>649.6481323242188</v>
       </c>
       <c r="D75" t="n">
-        <v>652.5999755859375</v>
+        <v>650.7050520182237</v>
       </c>
       <c r="E75" t="n">
-        <v>649.1699829101562</v>
+        <v>647.2850188493404</v>
       </c>
       <c r="F75" t="n">
-        <v>651.6199951171875</v>
+        <v>649.7279170722375</v>
       </c>
       <c r="G75" t="n">
         <v>6384100</v>
@@ -2174,16 +2174,16 @@
         <v>46133</v>
       </c>
       <c r="C76" t="n">
-        <v>647.25</v>
+        <v>645.37060546875</v>
       </c>
       <c r="D76" t="n">
-        <v>653.8599853515625</v>
+        <v>651.9613976641574</v>
       </c>
       <c r="E76" t="n">
-        <v>645.9400024414062</v>
+        <v>644.064411698874</v>
       </c>
       <c r="F76" t="n">
-        <v>652.9400024414062</v>
+        <v>651.0440860724256</v>
       </c>
       <c r="G76" t="n">
         <v>8514900</v>
@@ -2197,16 +2197,16 @@
         <v>46134</v>
       </c>
       <c r="C77" t="n">
-        <v>653.9000244140625</v>
+        <v>652.0013427734375</v>
       </c>
       <c r="D77" t="n">
-        <v>654.1900024414062</v>
+        <v>652.2904788128074</v>
       </c>
       <c r="E77" t="n">
-        <v>651.0900268554688</v>
+        <v>649.1995043990852</v>
       </c>
       <c r="F77" t="n">
-        <v>651.97998046875</v>
+        <v>650.086873919197</v>
       </c>
       <c r="G77" t="n">
         <v>4537200</v>
@@ -2220,16 +2220,16 @@
         <v>46135</v>
       </c>
       <c r="C78" t="n">
-        <v>651.260009765625</v>
+        <v>649.3689575195312</v>
       </c>
       <c r="D78" t="n">
-        <v>654.9000244140625</v>
+        <v>652.9984027213983</v>
       </c>
       <c r="E78" t="n">
-        <v>645.6599731445312</v>
+        <v>643.7851816263676</v>
       </c>
       <c r="F78" t="n">
-        <v>652.22998046875</v>
+        <v>650.3361117357704</v>
       </c>
       <c r="G78" t="n">
         <v>6519500</v>
@@ -2243,16 +2243,16 @@
         <v>46136</v>
       </c>
       <c r="C79" t="n">
-        <v>656.4199829101562</v>
+        <v>654.5139770507812</v>
       </c>
       <c r="D79" t="n">
-        <v>656.8200073242188</v>
+        <v>654.9128399388437</v>
       </c>
       <c r="E79" t="n">
-        <v>651.8200073242188</v>
+        <v>649.9273581277243</v>
       </c>
       <c r="F79" t="n">
-        <v>653.4000244140625</v>
+        <v>651.5027874202591</v>
       </c>
       <c r="G79" t="n">
         <v>4793800</v>
@@ -2266,16 +2266,16 @@
         <v>46139</v>
       </c>
       <c r="C80" t="n">
-        <v>657.5</v>
+        <v>655.5908813476562</v>
       </c>
       <c r="D80" t="n">
-        <v>657.9000244140625</v>
+        <v>655.9897442498248</v>
       </c>
       <c r="E80" t="n">
-        <v>654.8400268554688</v>
+        <v>652.9386317078322</v>
       </c>
       <c r="F80" t="n">
-        <v>655.6699829101562</v>
+        <v>653.7661779000335</v>
       </c>
       <c r="G80" t="n">
         <v>5319200</v>
@@ -2289,16 +2289,16 @@
         <v>46140</v>
       </c>
       <c r="C81" t="n">
-        <v>654.260009765625</v>
+        <v>652.3602905273438</v>
       </c>
       <c r="D81" t="n">
-        <v>655.3900146484375</v>
+        <v>653.4870143109248</v>
       </c>
       <c r="E81" t="n">
-        <v>652.010009765625</v>
+        <v>650.1168236613001</v>
       </c>
       <c r="F81" t="n">
-        <v>654.4099731445312</v>
+        <v>652.5098184703198</v>
       </c>
       <c r="G81" t="n">
         <v>5527100</v>
@@ -2312,16 +2312,16 @@
         <v>46141</v>
       </c>
       <c r="C82" t="n">
-        <v>654.239990234375</v>
+        <v>652.34033203125</v>
       </c>
       <c r="D82" t="n">
-        <v>654.719970703125</v>
+        <v>652.8189188235992</v>
       </c>
       <c r="E82" t="n">
-        <v>651.260009765625</v>
+        <v>649.3690042655251</v>
       </c>
       <c r="F82" t="n">
-        <v>653.6199951171875</v>
+        <v>651.7221371384875</v>
       </c>
       <c r="G82" t="n">
         <v>6302000</v>
@@ -2335,16 +2335,16 @@
         <v>46142</v>
       </c>
       <c r="C83" t="n">
-        <v>660.5800170898438</v>
+        <v>658.6619262695312</v>
       </c>
       <c r="D83" t="n">
-        <v>661.77001953125</v>
+        <v>659.8484733645753</v>
       </c>
       <c r="E83" t="n">
-        <v>653.1500244140625</v>
+        <v>651.2535076655925</v>
       </c>
       <c r="F83" t="n">
-        <v>657</v>
+        <v>655.0923042835946</v>
       </c>
       <c r="G83" t="n">
         <v>5948400</v>
@@ -2358,16 +2358,16 @@
         <v>46143</v>
       </c>
       <c r="C84" t="n">
-        <v>662.52001953125</v>
+        <v>660.5963134765625</v>
       </c>
       <c r="D84" t="n">
-        <v>666.4199829101562</v>
+        <v>664.4849528457122</v>
       </c>
       <c r="E84" t="n">
-        <v>662.3800048828125</v>
+        <v>660.4567053773899</v>
       </c>
       <c r="F84" t="n">
-        <v>663.0900268554688</v>
+        <v>661.1646657163936</v>
       </c>
       <c r="G84" t="n">
         <v>5426500</v>
@@ -2381,16 +2381,16 @@
         <v>46146</v>
       </c>
       <c r="C85" t="n">
-        <v>660.1199951171875</v>
+        <v>658.2032470703125</v>
       </c>
       <c r="D85" t="n">
-        <v>663.8499755859375</v>
+        <v>661.9223970342584</v>
       </c>
       <c r="E85" t="n">
-        <v>657.3900146484375</v>
+        <v>655.4811934705715</v>
       </c>
       <c r="F85" t="n">
-        <v>661.989990234375</v>
+        <v>660.0678124027411</v>
       </c>
       <c r="G85" t="n">
         <v>5962400</v>
@@ -2404,16 +2404,16 @@
         <v>46147</v>
       </c>
       <c r="C86" t="n">
-        <v>665.2999877929688</v>
+        <v>663.3682250976562</v>
       </c>
       <c r="D86" t="n">
-        <v>666.5499877929688</v>
+        <v>664.6145956020702</v>
       </c>
       <c r="E86" t="n">
-        <v>663.3300170898438</v>
+        <v>661.4039743945087</v>
       </c>
       <c r="F86" t="n">
-        <v>663.5800170898438</v>
+        <v>661.6532484953915</v>
       </c>
       <c r="G86" t="n">
         <v>5052600</v>
@@ -2427,16 +2427,16 @@
         <v>46148</v>
       </c>
       <c r="C87" t="n">
-        <v>674.6599731445312</v>
+        <v>672.7009887695312</v>
       </c>
       <c r="D87" t="n">
-        <v>675.3400268554688</v>
+        <v>673.3790678345035</v>
       </c>
       <c r="E87" t="n">
-        <v>669.1500244140625</v>
+        <v>667.2070390665722</v>
       </c>
       <c r="F87" t="n">
-        <v>669.4500122070312</v>
+        <v>667.5061557964536</v>
       </c>
       <c r="G87" t="n">
         <v>6441500</v>
@@ -2450,16 +2450,16 @@
         <v>46149</v>
       </c>
       <c r="C88" t="n">
-        <v>672.5399780273438</v>
+        <v>670.587158203125</v>
       </c>
       <c r="D88" t="n">
-        <v>676.760009765625</v>
+        <v>674.7949364517899</v>
       </c>
       <c r="E88" t="n">
-        <v>670.9199829101562</v>
+        <v>668.9718669826326</v>
       </c>
       <c r="F88" t="n">
-        <v>675.8200073242188</v>
+        <v>673.8576634472385</v>
       </c>
       <c r="G88" t="n">
         <v>6260300</v>
@@ -2473,16 +2473,16 @@
         <v>46150</v>
       </c>
       <c r="C89" t="n">
-        <v>678.0399780273438</v>
+        <v>676.0711669921875</v>
       </c>
       <c r="D89" t="n">
-        <v>678.530029296875</v>
+        <v>676.5597953097122</v>
       </c>
       <c r="E89" t="n">
-        <v>675.3699951171875</v>
+        <v>673.4089368576604</v>
       </c>
       <c r="F89" t="n">
-        <v>675.7000122070312</v>
+        <v>673.7379956835236</v>
       </c>
       <c r="G89" t="n">
         <v>4348100</v>
@@ -2496,16 +2496,16 @@
         <v>46153</v>
       </c>
       <c r="C90" t="n">
-        <v>679.52001953125</v>
+        <v>677.5469360351562</v>
       </c>
       <c r="D90" t="n">
-        <v>681.0599975585938</v>
+        <v>679.0824425161985</v>
       </c>
       <c r="E90" t="n">
-        <v>677.0800170898438</v>
+        <v>675.1140184895723</v>
       </c>
       <c r="F90" t="n">
-        <v>677.0800170898438</v>
+        <v>675.1140184895723</v>
       </c>
       <c r="G90" t="n">
         <v>5693400</v>
@@ -2519,16 +2519,16 @@
         <v>46154</v>
       </c>
       <c r="C91" t="n">
-        <v>678.6699829101562</v>
+        <v>676.6993408203125</v>
       </c>
       <c r="D91" t="n">
-        <v>679.260009765625</v>
+        <v>677.2876544251811</v>
       </c>
       <c r="E91" t="n">
-        <v>672.7999877929688</v>
+        <v>670.8463903046786</v>
       </c>
       <c r="F91" t="n">
-        <v>677.469970703125</v>
+        <v>675.5028130676155</v>
       </c>
       <c r="G91" t="n">
         <v>6073400</v>
@@ -2542,16 +2542,16 @@
         <v>46155</v>
       </c>
       <c r="C92" t="n">
-        <v>682.4099731445312</v>
+        <v>680.4285278320312</v>
       </c>
       <c r="D92" t="n">
-        <v>683.9099731445312</v>
+        <v>681.9241724326588</v>
       </c>
       <c r="E92" t="n">
-        <v>676.2000122070312</v>
+        <v>674.236598134511</v>
       </c>
       <c r="F92" t="n">
-        <v>678.9000244140625</v>
+        <v>676.9287705872277</v>
       </c>
       <c r="G92" t="n">
         <v>4918000</v>
@@ -2565,16 +2565,16 @@
         <v>46156</v>
       </c>
       <c r="C93" t="n">
-        <v>687.72998046875</v>
+        <v>685.7330322265625</v>
       </c>
       <c r="D93" t="n">
-        <v>689.0999755859375</v>
+        <v>687.0990493154267</v>
       </c>
       <c r="E93" t="n">
-        <v>683.6599731445312</v>
+        <v>681.6748429038888</v>
       </c>
       <c r="F93" t="n">
-        <v>683.739990234375</v>
+        <v>681.7546276496565</v>
       </c>
       <c r="G93" t="n">
         <v>5370000</v>
@@ -2588,16 +2588,16 @@
         <v>46157</v>
       </c>
       <c r="C94" t="n">
-        <v>679.4400024414062</v>
+        <v>677.4671630859375</v>
       </c>
       <c r="D94" t="n">
-        <v>683.52001953125</v>
+        <v>681.5353333338866</v>
       </c>
       <c r="E94" t="n">
-        <v>678.4400024414062</v>
+        <v>676.4700667114944</v>
       </c>
       <c r="F94" t="n">
-        <v>682.0399780273438</v>
+        <v>680.0595893163164</v>
       </c>
       <c r="G94" t="n">
         <v>6448500</v>
@@ -2611,16 +2611,16 @@
         <v>46160</v>
       </c>
       <c r="C95" t="n">
-        <v>678.9099731445312</v>
+        <v>676.9386596679688</v>
       </c>
       <c r="D95" t="n">
-        <v>681.6099853515625</v>
+        <v>679.6308319983431</v>
       </c>
       <c r="E95" t="n">
-        <v>674.25</v>
+        <v>672.2922174306617</v>
       </c>
       <c r="F95" t="n">
-        <v>680.1799926757812</v>
+        <v>678.2049915134924</v>
       </c>
       <c r="G95" t="n">
         <v>7585400</v>
@@ -2634,16 +2634,16 @@
         <v>46161</v>
       </c>
       <c r="C96" t="n">
-        <v>674.5900268554688</v>
+        <v>672.6312866210938</v>
       </c>
       <c r="D96" t="n">
-        <v>678.1500244140625</v>
+        <v>676.1809473674391</v>
       </c>
       <c r="E96" t="n">
-        <v>672.5499877929688</v>
+        <v>670.5971710179281</v>
       </c>
       <c r="F96" t="n">
-        <v>675.5599975585938</v>
+        <v>673.5984409163759</v>
       </c>
       <c r="G96" t="n">
         <v>5664200</v>
@@ -2657,16 +2657,16 @@
         <v>46162</v>
       </c>
       <c r="C97" t="n">
-        <v>681.5700073242188</v>
+        <v>679.5910034179688</v>
       </c>
       <c r="D97" t="n">
-        <v>682</v>
+        <v>680.0197475687622</v>
       </c>
       <c r="E97" t="n">
-        <v>674.739990234375</v>
+        <v>672.7808179380188</v>
       </c>
       <c r="F97" t="n">
-        <v>676.3200073242188</v>
+        <v>674.3562472966549</v>
       </c>
       <c r="G97" t="n">
         <v>5506800</v>
@@ -2680,16 +2680,16 @@
         <v>46163</v>
       </c>
       <c r="C98" t="n">
-        <v>682.8400268554688</v>
+        <v>680.8572998046875</v>
       </c>
       <c r="D98" t="n">
-        <v>684.8300170898438</v>
+        <v>682.8415118079786</v>
       </c>
       <c r="E98" t="n">
-        <v>677.6199951171875</v>
+        <v>675.6524252009126</v>
       </c>
       <c r="F98" t="n">
-        <v>679.0800170898438</v>
+        <v>677.1082077837469</v>
       </c>
       <c r="G98" t="n">
         <v>7335400</v>
@@ -2703,16 +2703,16 @@
         <v>46164</v>
       </c>
       <c r="C99" t="n">
-        <v>685.5499877929688</v>
+        <v>683.5593872070312</v>
       </c>
       <c r="D99" t="n">
-        <v>688.5800170898438</v>
+        <v>686.5806183444705</v>
       </c>
       <c r="E99" t="n">
-        <v>684.47998046875</v>
+        <v>682.4924868148298</v>
       </c>
       <c r="F99" t="n">
-        <v>686.0999755859375</v>
+        <v>684.1077780252463</v>
       </c>
       <c r="G99" t="n">
         <v>4319800</v>
@@ -2726,16 +2726,16 @@
         <v>46168</v>
       </c>
       <c r="C100" t="n">
-        <v>690.010009765625</v>
+        <v>688.0064697265625</v>
       </c>
       <c r="D100" t="n">
-        <v>691.510009765625</v>
+        <v>689.5021142679227</v>
       </c>
       <c r="E100" t="n">
-        <v>688.0800170898438</v>
+        <v>686.0820810529642</v>
       </c>
       <c r="F100" t="n">
-        <v>689.6500244140625</v>
+        <v>687.6475296425398</v>
       </c>
       <c r="G100" t="n">
         <v>6633800</v>
@@ -2749,16 +2749,16 @@
         <v>46169</v>
       </c>
       <c r="C101" t="n">
-        <v>689.9600219726562</v>
+        <v>687.9566040039062</v>
       </c>
       <c r="D101" t="n">
-        <v>690.780029296875</v>
+        <v>688.7742302953759</v>
       </c>
       <c r="E101" t="n">
-        <v>687.9199829101562</v>
+        <v>685.9224885468103</v>
       </c>
       <c r="F101" t="n">
-        <v>690.3599853515625</v>
+        <v>688.3554060201326</v>
       </c>
       <c r="G101" t="n">
         <v>7386500</v>
@@ -2772,16 +2772,16 @@
         <v>46170</v>
       </c>
       <c r="C102" t="n">
-        <v>693.9099731445312</v>
+        <v>691.8950805664062</v>
       </c>
       <c r="D102" t="n">
-        <v>694.2899780273438</v>
+        <v>692.2739820366038</v>
       </c>
       <c r="E102" t="n">
-        <v>688.8499755859375</v>
+        <v>686.8497756220142</v>
       </c>
       <c r="F102" t="n">
-        <v>689.760009765625</v>
+        <v>687.7571673535666</v>
       </c>
       <c r="G102" t="n">
         <v>8477100</v>
@@ -2795,16 +2795,16 @@
         <v>46171</v>
       </c>
       <c r="C103" t="n">
-        <v>695.489990234375</v>
+        <v>693.4705200195312</v>
       </c>
       <c r="D103" t="n">
-        <v>697</v>
+        <v>694.9761452220588</v>
       </c>
       <c r="E103" t="n">
-        <v>693.8900146484375</v>
+        <v>691.87519022733</v>
       </c>
       <c r="F103" t="n">
-        <v>695</v>
+        <v>692.981952552842</v>
       </c>
       <c r="G103" t="n">
         <v>5080400</v>
@@ -2818,16 +2818,16 @@
         <v>46174</v>
       </c>
       <c r="C104" t="n">
-        <v>697.2999877929688</v>
+        <v>695.2752685546875</v>
       </c>
       <c r="D104" t="n">
-        <v>699.0599975585938</v>
+        <v>697.0301678575355</v>
       </c>
       <c r="E104" t="n">
-        <v>693.9400024414062</v>
+        <v>691.9250394444856</v>
       </c>
       <c r="F104" t="n">
-        <v>694.5399780273438</v>
+        <v>692.5232729077605</v>
       </c>
       <c r="G104" t="n">
         <v>10051200</v>
@@ -2841,16 +2841,16 @@
         <v>46175</v>
       </c>
       <c r="C105" t="n">
-        <v>698.260009765625</v>
+        <v>696.2325439453125</v>
       </c>
       <c r="D105" t="n">
-        <v>699.1500244140625</v>
+        <v>697.1199743496946</v>
       </c>
       <c r="E105" t="n">
-        <v>695.780029296875</v>
+        <v>693.759764340947</v>
       </c>
       <c r="F105" t="n">
-        <v>696.0599975585938</v>
+        <v>694.0389196876005</v>
       </c>
       <c r="G105" t="n">
         <v>4750700</v>
@@ -2864,16 +2864,16 @@
         <v>46176</v>
       </c>
       <c r="C106" t="n">
-        <v>693.3599853515625</v>
+        <v>691.3467407226562</v>
       </c>
       <c r="D106" t="n">
-        <v>697.6500244140625</v>
+        <v>695.6243231994247</v>
       </c>
       <c r="E106" t="n">
-        <v>692.8499755859375</v>
+        <v>690.8382118247522</v>
       </c>
       <c r="F106" t="n">
-        <v>697.0800170898438</v>
+        <v>695.055970952234</v>
       </c>
       <c r="G106" t="n">
         <v>5970400</v>
@@ -2887,16 +2887,16 @@
         <v>46177</v>
       </c>
       <c r="C107" t="n">
-        <v>696.0599975585938</v>
+        <v>694.0388793945312</v>
       </c>
       <c r="D107" t="n">
-        <v>697.2000122070312</v>
+        <v>695.1755838336171</v>
       </c>
       <c r="E107" t="n">
-        <v>690.9000244140625</v>
+        <v>688.8938890323536</v>
       </c>
       <c r="F107" t="n">
-        <v>691.489990234375</v>
+        <v>689.4821417954013</v>
       </c>
       <c r="G107" t="n">
         <v>6630000</v>
@@ -2910,16 +2910,16 @@
         <v>46178</v>
       </c>
       <c r="C108" t="n">
-        <v>678</v>
+        <v>676.0313110351562</v>
       </c>
       <c r="D108" t="n">
-        <v>692.1799926757812</v>
+        <v>690.1701296768632</v>
       </c>
       <c r="E108" t="n">
-        <v>676.25</v>
+        <v>674.2863924594756</v>
       </c>
       <c r="F108" t="n">
-        <v>691.7100219726562</v>
+        <v>689.7015236140584</v>
       </c>
       <c r="G108" t="n">
         <v>10846500</v>
@@ -2933,16 +2933,16 @@
         <v>46181</v>
       </c>
       <c r="C109" t="n">
-        <v>679.6799926757812</v>
+        <v>677.7064208984375</v>
       </c>
       <c r="D109" t="n">
-        <v>685.2899780273438</v>
+        <v>683.3001166594861</v>
       </c>
       <c r="E109" t="n">
-        <v>678.7000122070312</v>
+        <v>676.7292859773222</v>
       </c>
       <c r="F109" t="n">
-        <v>683.469970703125</v>
+        <v>681.485394050322</v>
       </c>
       <c r="G109" t="n">
         <v>8867200</v>
@@ -2956,16 +2956,16 @@
         <v>46182</v>
       </c>
       <c r="C110" t="n">
-        <v>677.7000122070312</v>
+        <v>675.7322387695312</v>
       </c>
       <c r="D110" t="n">
-        <v>686.760009765625</v>
+        <v>684.7659296699894</v>
       </c>
       <c r="E110" t="n">
-        <v>664.3200073242188</v>
+        <v>662.3910841415923</v>
       </c>
       <c r="F110" t="n">
-        <v>683.7100219726562</v>
+        <v>681.7247978381474</v>
       </c>
       <c r="G110" t="n">
         <v>16197200</v>
@@ -2979,16 +2979,16 @@
         <v>46183</v>
       </c>
       <c r="C111" t="n">
-        <v>667.0499877929688</v>
+        <v>665.1130981445312</v>
       </c>
       <c r="D111" t="n">
-        <v>678.8800048828125</v>
+        <v>676.908764828766</v>
       </c>
       <c r="E111" t="n">
-        <v>666.8800048828125</v>
+        <v>664.943608807788</v>
       </c>
       <c r="F111" t="n">
-        <v>674.3200073242188</v>
+        <v>672.3620079751116</v>
       </c>
       <c r="G111" t="n">
         <v>16472700</v>
@@ -3002,16 +3002,16 @@
         <v>46184</v>
       </c>
       <c r="C112" t="n">
-        <v>678.22998046875</v>
+        <v>676.2606201171875</v>
       </c>
       <c r="D112" t="n">
-        <v>680.3800048828125</v>
+        <v>678.4044015562152</v>
       </c>
       <c r="E112" t="n">
-        <v>666</v>
+        <v>664.066151553439</v>
       </c>
       <c r="F112" t="n">
-        <v>670.0999755859375</v>
+        <v>668.1542221372476</v>
       </c>
       <c r="G112" t="n">
         <v>19974200</v>
@@ -3025,16 +3025,16 @@
         <v>46185</v>
       </c>
       <c r="C113" t="n">
-        <v>681.9500122070312</v>
+        <v>679.9698486328125</v>
       </c>
       <c r="D113" t="n">
-        <v>684.4400024414062</v>
+        <v>682.452608736131</v>
       </c>
       <c r="E113" t="n">
-        <v>675.8099975585938</v>
+        <v>673.8476626127706</v>
       </c>
       <c r="F113" t="n">
-        <v>681.0800170898438</v>
+        <v>679.1023797017236</v>
       </c>
       <c r="G113" t="n">
         <v>6328000</v>
@@ -3048,16 +3048,16 @@
         <v>46188</v>
       </c>
       <c r="C114" t="n">
-        <v>693.8300170898438</v>
+        <v>691.8153686523438</v>
       </c>
       <c r="D114" t="n">
-        <v>695.75</v>
+        <v>693.7297765794715</v>
       </c>
       <c r="E114" t="n">
-        <v>691.260009765625</v>
+        <v>689.2528237628894</v>
       </c>
       <c r="F114" t="n">
-        <v>691.2999877929688</v>
+        <v>689.2926857075207</v>
       </c>
       <c r="G114" t="n">
         <v>14068900</v>
@@ -3071,16 +3071,16 @@
         <v>46189</v>
       </c>
       <c r="C115" t="n">
-        <v>689.75</v>
+        <v>687.7471923828125</v>
       </c>
       <c r="D115" t="n">
-        <v>694.5700073242188</v>
+        <v>692.5532039877361</v>
       </c>
       <c r="E115" t="n">
-        <v>689.4400024414062</v>
+        <v>687.4380949553847</v>
       </c>
       <c r="F115" t="n">
-        <v>693.8300170898438</v>
+        <v>691.8153624421296</v>
       </c>
       <c r="G115" t="n">
         <v>13324100</v>
@@ -3094,16 +3094,16 @@
         <v>46190</v>
       </c>
       <c r="C116" t="n">
-        <v>681.4099731445312</v>
+        <v>679.431396484375</v>
       </c>
       <c r="D116" t="n">
-        <v>691.530029296875</v>
+        <v>689.5220675268852</v>
       </c>
       <c r="E116" t="n">
-        <v>679.6400146484375</v>
+        <v>677.6665773298051</v>
       </c>
       <c r="F116" t="n">
-        <v>690.760009765625</v>
+        <v>688.7542838635158</v>
       </c>
       <c r="G116" t="n">
         <v>15029600</v>
@@ -3117,16 +3117,16 @@
         <v>46191</v>
       </c>
       <c r="C117" t="n">
-        <v>688.1099853515625</v>
+        <v>686.1119384765625</v>
       </c>
       <c r="D117" t="n">
-        <v>689.7000122070312</v>
+        <v>687.6973484128507</v>
       </c>
       <c r="E117" t="n">
-        <v>685.7000122070312</v>
+        <v>683.7089631076961</v>
       </c>
       <c r="F117" t="n">
-        <v>689.2999877929688</v>
+        <v>687.2984855391632</v>
       </c>
       <c r="G117" t="n">
         <v>17747900</v>
@@ -3140,19 +3140,226 @@
         <v>46195</v>
       </c>
       <c r="C118" t="n">
-        <v>686.0999755859375</v>
+        <v>684.1077880859375</v>
       </c>
       <c r="D118" t="n">
-        <v>691.5</v>
+        <v>689.4921327717968</v>
       </c>
       <c r="E118" t="n">
-        <v>685</v>
+        <v>683.0110064333779</v>
       </c>
       <c r="F118" t="n">
-        <v>689.1699829101562</v>
+        <v>687.1688812133426</v>
       </c>
       <c r="G118" t="n">
-        <v>5565075</v>
+        <v>13367200</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C119" t="n">
+        <v>674.3761596679688</v>
+      </c>
+      <c r="D119" t="n">
+        <v>679.7504626430755</v>
+      </c>
+      <c r="E119" t="n">
+        <v>673.0599852073517</v>
+      </c>
+      <c r="F119" t="n">
+        <v>674.3960602112073</v>
+      </c>
+      <c r="G119" t="n">
+        <v>17581700</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C120" t="n">
+        <v>673.72802734375</v>
+      </c>
+      <c r="D120" t="n">
+        <v>680.0895068515269</v>
+      </c>
+      <c r="E120" t="n">
+        <v>671.7238539662496</v>
+      </c>
+      <c r="F120" t="n">
+        <v>675.712239319944</v>
+      </c>
+      <c r="G120" t="n">
+        <v>9677000</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C121" t="n">
+        <v>673.7479858398438</v>
+      </c>
+      <c r="D121" t="n">
+        <v>679.5610136500771</v>
+      </c>
+      <c r="E121" t="n">
+        <v>670.6270694454009</v>
+      </c>
+      <c r="F121" t="n">
+        <v>679.1622116311859</v>
+      </c>
+      <c r="G121" t="n">
+        <v>26266500</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C122" t="n">
+        <v>670.260009765625</v>
+      </c>
+      <c r="D122" t="n">
+        <v>676.9600219726562</v>
+      </c>
+      <c r="E122" t="n">
+        <v>668.0999755859375</v>
+      </c>
+      <c r="F122" t="n">
+        <v>669.9600219726562</v>
+      </c>
+      <c r="G122" t="n">
+        <v>6007600</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C123" t="n">
+        <v>681.010009765625</v>
+      </c>
+      <c r="D123" t="n">
+        <v>681.5700073242188</v>
+      </c>
+      <c r="E123" t="n">
+        <v>672.9299926757812</v>
+      </c>
+      <c r="F123" t="n">
+        <v>677.010009765625</v>
+      </c>
+      <c r="G123" t="n">
+        <v>5703800</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C124" t="n">
+        <v>686.8099975585938</v>
+      </c>
+      <c r="D124" t="n">
+        <v>687.530029296875</v>
+      </c>
+      <c r="E124" t="n">
+        <v>680.989990234375</v>
+      </c>
+      <c r="F124" t="n">
+        <v>681.3200073242188</v>
+      </c>
+      <c r="G124" t="n">
+        <v>9892400</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C125" t="n">
+        <v>685.4600219726562</v>
+      </c>
+      <c r="D125" t="n">
+        <v>688.8300170898438</v>
+      </c>
+      <c r="E125" t="n">
+        <v>682.2999877929688</v>
+      </c>
+      <c r="F125" t="n">
+        <v>684.72998046875</v>
+      </c>
+      <c r="G125" t="n">
+        <v>8659300</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C126" t="n">
+        <v>684.8400268554688</v>
+      </c>
+      <c r="D126" t="n">
+        <v>690.5</v>
+      </c>
+      <c r="E126" t="n">
+        <v>680.219970703125</v>
+      </c>
+      <c r="F126" t="n">
+        <v>686.97998046875</v>
+      </c>
+      <c r="G126" t="n">
+        <v>6994700</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="C127" t="n">
+        <v>690.6199951171875</v>
+      </c>
+      <c r="D127" t="n">
+        <v>691.5750122070312</v>
+      </c>
+      <c r="E127" t="n">
+        <v>687</v>
+      </c>
+      <c r="F127" t="n">
+        <v>688.1099853515625</v>
+      </c>
+      <c r="G127" t="n">
+        <v>5526317</v>
       </c>
     </row>
   </sheetData>

--- a/Data/voo.xlsx
+++ b/Data/voo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,16 +495,16 @@
         <v>46027</v>
       </c>
       <c r="C3" t="n">
-        <v>628.6392822265625</v>
+        <v>628.6392211914062</v>
       </c>
       <c r="D3" t="n">
-        <v>630.2096936449323</v>
+        <v>630.2096324573033</v>
       </c>
       <c r="E3" t="n">
-        <v>627.4166714981994</v>
+        <v>627.4166105817476</v>
       </c>
       <c r="F3" t="n">
-        <v>627.5657896032119</v>
+        <v>627.565728672282</v>
       </c>
       <c r="G3" t="n">
         <v>16175600</v>
@@ -541,16 +541,16 @@
         <v>46029</v>
       </c>
       <c r="C5" t="n">
-        <v>630.3388671875</v>
+        <v>630.3388061523438</v>
       </c>
       <c r="D5" t="n">
-        <v>634.364388398435</v>
+        <v>634.3643269734911</v>
       </c>
       <c r="E5" t="n">
-        <v>630.1003267700273</v>
+        <v>630.1002657579688</v>
       </c>
       <c r="F5" t="n">
-        <v>632.7343419902274</v>
+        <v>632.7342807231195</v>
       </c>
       <c r="G5" t="n">
         <v>8820100</v>
@@ -587,16 +587,16 @@
         <v>46031</v>
       </c>
       <c r="C7" t="n">
-        <v>634.453857421875</v>
+        <v>634.4539184570312</v>
       </c>
       <c r="D7" t="n">
-        <v>635.5770357514454</v>
+        <v>635.5770968946526</v>
       </c>
       <c r="E7" t="n">
-        <v>629.9710933985081</v>
+        <v>629.9711540024175</v>
       </c>
       <c r="F7" t="n">
-        <v>631.3129742169032</v>
+        <v>631.313034949903</v>
       </c>
       <c r="G7" t="n">
         <v>7864100</v>
@@ -610,16 +610,16 @@
         <v>46034</v>
       </c>
       <c r="C8" t="n">
-        <v>635.4776611328125</v>
+        <v>635.4777221679688</v>
       </c>
       <c r="D8" t="n">
-        <v>636.2926539819083</v>
+        <v>636.2927150953415</v>
       </c>
       <c r="E8" t="n">
-        <v>631.3228598626637</v>
+        <v>631.3229204987674</v>
       </c>
       <c r="F8" t="n">
-        <v>631.3527077472665</v>
+        <v>631.3527683862371</v>
       </c>
       <c r="G8" t="n">
         <v>7929800</v>
@@ -679,16 +679,16 @@
         <v>46037</v>
       </c>
       <c r="C11" t="n">
-        <v>632.7740478515625</v>
+        <v>632.7741088867188</v>
       </c>
       <c r="D11" t="n">
-        <v>635.7161877462142</v>
+        <v>635.716249065159</v>
       </c>
       <c r="E11" t="n">
-        <v>631.8596227400693</v>
+        <v>631.8596836870233</v>
       </c>
       <c r="F11" t="n">
-        <v>634.911083543028</v>
+        <v>634.9111447843152</v>
       </c>
       <c r="G11" t="n">
         <v>6937000</v>
@@ -863,16 +863,16 @@
         <v>46050</v>
       </c>
       <c r="C19" t="n">
-        <v>635.736083984375</v>
+        <v>635.7360229492188</v>
       </c>
       <c r="D19" t="n">
-        <v>637.9327549788177</v>
+        <v>637.9326937327655</v>
       </c>
       <c r="E19" t="n">
-        <v>634.3644158580984</v>
+        <v>634.3643549546319</v>
       </c>
       <c r="F19" t="n">
-        <v>637.1773365131655</v>
+        <v>637.1772753396389</v>
       </c>
       <c r="G19" t="n">
         <v>5568700</v>
@@ -1001,16 +1001,16 @@
         <v>46058</v>
       </c>
       <c r="C25" t="n">
-        <v>619.335693359375</v>
+        <v>619.3357543945312</v>
       </c>
       <c r="D25" t="n">
-        <v>624.9515847493406</v>
+        <v>624.9516463379395</v>
       </c>
       <c r="E25" t="n">
-        <v>617.7453835733044</v>
+        <v>617.7454444517366</v>
       </c>
       <c r="F25" t="n">
-        <v>622.456738497629</v>
+        <v>622.4567998403622</v>
       </c>
       <c r="G25" t="n">
         <v>11714700</v>
@@ -1070,16 +1070,16 @@
         <v>46063</v>
       </c>
       <c r="C28" t="n">
-        <v>632.59521484375</v>
+        <v>632.5951538085938</v>
       </c>
       <c r="D28" t="n">
-        <v>636.7499558321192</v>
+        <v>636.7498943960981</v>
       </c>
       <c r="E28" t="n">
-        <v>632.2374041939814</v>
+        <v>632.237343193348</v>
       </c>
       <c r="F28" t="n">
-        <v>635.2789160498899</v>
+        <v>635.2788547558001</v>
       </c>
       <c r="G28" t="n">
         <v>13645300</v>
@@ -1116,16 +1116,16 @@
         <v>46065</v>
       </c>
       <c r="C30" t="n">
-        <v>622.705322265625</v>
+        <v>622.7052612304688</v>
       </c>
       <c r="D30" t="n">
-        <v>635.656636283277</v>
+        <v>635.6565739786832</v>
       </c>
       <c r="E30" t="n">
-        <v>621.9797516577522</v>
+        <v>621.9796906937136</v>
       </c>
       <c r="F30" t="n">
-        <v>634.652728054257</v>
+        <v>634.6526658480624</v>
       </c>
       <c r="G30" t="n">
         <v>8951100</v>
@@ -1300,16 +1300,16 @@
         <v>46078</v>
       </c>
       <c r="C38" t="n">
-        <v>633.6785888671875</v>
+        <v>633.6786499023438</v>
       </c>
       <c r="D38" t="n">
-        <v>634.1457203877115</v>
+        <v>634.1457814678613</v>
       </c>
       <c r="E38" t="n">
-        <v>630.9054049624871</v>
+        <v>630.9054657305335</v>
       </c>
       <c r="F38" t="n">
-        <v>630.9352528466555</v>
+        <v>630.935313617577</v>
       </c>
       <c r="G38" t="n">
         <v>12135200</v>
@@ -1346,16 +1346,16 @@
         <v>46080</v>
       </c>
       <c r="C40" t="n">
-        <v>627.227783203125</v>
+        <v>627.2277221679688</v>
       </c>
       <c r="D40" t="n">
-        <v>627.8738807349088</v>
+        <v>627.8738196368811</v>
       </c>
       <c r="E40" t="n">
-        <v>623.1525761045295</v>
+        <v>623.1525154659292</v>
       </c>
       <c r="F40" t="n">
-        <v>624.4447105016621</v>
+        <v>624.444649737325</v>
       </c>
       <c r="G40" t="n">
         <v>10471100</v>
@@ -1438,16 +1438,16 @@
         <v>46086</v>
       </c>
       <c r="C44" t="n">
-        <v>623.0233154296875</v>
+        <v>623.0233764648438</v>
       </c>
       <c r="D44" t="n">
-        <v>626.6910258426402</v>
+        <v>626.6910872371077</v>
       </c>
       <c r="E44" t="n">
-        <v>617.646024993958</v>
+        <v>617.6460855023222</v>
       </c>
       <c r="F44" t="n">
-        <v>623.5003962422892</v>
+        <v>623.5004573241831</v>
       </c>
       <c r="G44" t="n">
         <v>12198800</v>
@@ -1484,16 +1484,16 @@
         <v>46090</v>
       </c>
       <c r="C46" t="n">
-        <v>620.031494140625</v>
+        <v>620.0315551757812</v>
       </c>
       <c r="D46" t="n">
-        <v>621.542330946535</v>
+        <v>621.5423921304164</v>
       </c>
       <c r="E46" t="n">
-        <v>605.5197197672502</v>
+        <v>605.5197793738849</v>
       </c>
       <c r="F46" t="n">
-        <v>609.1575823221168</v>
+        <v>609.1576422868583</v>
       </c>
       <c r="G46" t="n">
         <v>13929200</v>
@@ -1530,16 +1530,16 @@
         <v>46092</v>
       </c>
       <c r="C48" t="n">
-        <v>618.272216796875</v>
+        <v>618.2722778320312</v>
       </c>
       <c r="D48" t="n">
-        <v>621.6516402913978</v>
+        <v>621.651701660167</v>
       </c>
       <c r="E48" t="n">
-        <v>615.5586680402731</v>
+        <v>615.5587288075508</v>
       </c>
       <c r="F48" t="n">
-        <v>619.4351315974586</v>
+        <v>619.4351927474164</v>
       </c>
       <c r="G48" t="n">
         <v>6433300</v>
@@ -1553,16 +1553,16 @@
         <v>46093</v>
       </c>
       <c r="C49" t="n">
-        <v>608.7998046875</v>
+        <v>608.7997436523438</v>
       </c>
       <c r="D49" t="n">
-        <v>613.9783522130032</v>
+        <v>613.9782906586722</v>
       </c>
       <c r="E49" t="n">
-        <v>608.7202709917146</v>
+        <v>608.720209964532</v>
       </c>
       <c r="F49" t="n">
-        <v>613.491261409448</v>
+        <v>613.4911999039504</v>
       </c>
       <c r="G49" t="n">
         <v>15487600</v>
@@ -1599,16 +1599,16 @@
         <v>46097</v>
       </c>
       <c r="C51" t="n">
-        <v>611.4735717773438</v>
+        <v>611.4735107421875</v>
       </c>
       <c r="D51" t="n">
-        <v>614.3461275285033</v>
+        <v>614.3460662066185</v>
       </c>
       <c r="E51" t="n">
-        <v>609.8335153427746</v>
+        <v>609.8334544713231</v>
       </c>
       <c r="F51" t="n">
-        <v>611.006379552641</v>
+        <v>611.0063185641181</v>
       </c>
       <c r="G51" t="n">
         <v>8303200</v>
@@ -1622,16 +1622,16 @@
         <v>46098</v>
       </c>
       <c r="C52" t="n">
-        <v>613.1632690429688</v>
+        <v>613.163330078125</v>
       </c>
       <c r="D52" t="n">
-        <v>616.5228546969976</v>
+        <v>616.5229160665718</v>
       </c>
       <c r="E52" t="n">
-        <v>612.5470194298802</v>
+        <v>612.5470804036939</v>
       </c>
       <c r="F52" t="n">
-        <v>614.6343086785441</v>
+        <v>614.6343698601297</v>
       </c>
       <c r="G52" t="n">
         <v>9941800</v>
@@ -1714,16 +1714,16 @@
         <v>46104</v>
       </c>
       <c r="C56" t="n">
-        <v>600.778564453125</v>
+        <v>600.7785034179688</v>
       </c>
       <c r="D56" t="n">
-        <v>607.3387295253531</v>
+        <v>607.3386678237272</v>
       </c>
       <c r="E56" t="n">
-        <v>599.416845627479</v>
+        <v>599.4167847306644</v>
       </c>
       <c r="F56" t="n">
-        <v>603.1938772752512</v>
+        <v>603.193815994715</v>
       </c>
       <c r="G56" t="n">
         <v>24014300</v>
@@ -1737,16 +1737,16 @@
         <v>46105</v>
       </c>
       <c r="C57" t="n">
-        <v>598.7409057617188</v>
+        <v>598.740966796875</v>
       </c>
       <c r="D57" t="n">
-        <v>602.2495487731062</v>
+        <v>602.2496101659307</v>
       </c>
       <c r="E57" t="n">
-        <v>595.6993942656367</v>
+        <v>595.6994549907438</v>
       </c>
       <c r="F57" t="n">
-        <v>597.0014778647273</v>
+        <v>597.0015387225677</v>
       </c>
       <c r="G57" t="n">
         <v>18363300</v>
@@ -1760,16 +1760,16 @@
         <v>46106</v>
       </c>
       <c r="C58" t="n">
-        <v>602.0010375976562</v>
+        <v>602.0010986328125</v>
       </c>
       <c r="D58" t="n">
-        <v>605.7582308410098</v>
+        <v>605.7582922570971</v>
       </c>
       <c r="E58" t="n">
-        <v>599.7149445764509</v>
+        <v>599.7150053798267</v>
       </c>
       <c r="F58" t="n">
-        <v>603.7305768047668</v>
+        <v>603.730638015276</v>
       </c>
       <c r="G58" t="n">
         <v>23288300</v>
@@ -3350,7 +3350,7 @@
         <v>690.6199951171875</v>
       </c>
       <c r="D127" t="n">
-        <v>691.5750122070312</v>
+        <v>691.5800170898438</v>
       </c>
       <c r="E127" t="n">
         <v>687</v>
@@ -3359,7 +3359,99 @@
         <v>688.1099853515625</v>
       </c>
       <c r="G127" t="n">
-        <v>5526317</v>
+        <v>5610000</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C128" t="n">
+        <v>687.0800170898438</v>
+      </c>
+      <c r="D128" t="n">
+        <v>690.239990234375</v>
+      </c>
+      <c r="E128" t="n">
+        <v>684.989990234375</v>
+      </c>
+      <c r="F128" t="n">
+        <v>689.5800170898438</v>
+      </c>
+      <c r="G128" t="n">
+        <v>4847400</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C129" t="n">
+        <v>685.260009765625</v>
+      </c>
+      <c r="D129" t="n">
+        <v>685.8400268554688</v>
+      </c>
+      <c r="E129" t="n">
+        <v>679.72998046875</v>
+      </c>
+      <c r="F129" t="n">
+        <v>683.0999755859375</v>
+      </c>
+      <c r="G129" t="n">
+        <v>4839800</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C130" t="n">
+        <v>690.6900024414062</v>
+      </c>
+      <c r="D130" t="n">
+        <v>691.1900024414062</v>
+      </c>
+      <c r="E130" t="n">
+        <v>685.2899780273438</v>
+      </c>
+      <c r="F130" t="n">
+        <v>686.9500122070312</v>
+      </c>
+      <c r="G130" t="n">
+        <v>6423900</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C131" t="n">
+        <v>693.8599853515625</v>
+      </c>
+      <c r="D131" t="n">
+        <v>694.3300170898438</v>
+      </c>
+      <c r="E131" t="n">
+        <v>687.6300048828125</v>
+      </c>
+      <c r="F131" t="n">
+        <v>691.25</v>
+      </c>
+      <c r="G131" t="n">
+        <v>5318000</v>
       </c>
     </row>
   </sheetData>

--- a/Data/voo.xlsx
+++ b/Data/voo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,16 +495,16 @@
         <v>46027</v>
       </c>
       <c r="C3" t="n">
-        <v>628.6392211914062</v>
+        <v>628.6392822265625</v>
       </c>
       <c r="D3" t="n">
-        <v>630.2096324573033</v>
+        <v>630.2096936449323</v>
       </c>
       <c r="E3" t="n">
-        <v>627.4166105817476</v>
+        <v>627.4166714981994</v>
       </c>
       <c r="F3" t="n">
-        <v>627.565728672282</v>
+        <v>627.5657896032119</v>
       </c>
       <c r="G3" t="n">
         <v>16175600</v>
@@ -541,16 +541,16 @@
         <v>46029</v>
       </c>
       <c r="C5" t="n">
-        <v>630.3388061523438</v>
+        <v>630.3388671875</v>
       </c>
       <c r="D5" t="n">
-        <v>634.3643269734911</v>
+        <v>634.364388398435</v>
       </c>
       <c r="E5" t="n">
-        <v>630.1002657579688</v>
+        <v>630.1003267700273</v>
       </c>
       <c r="F5" t="n">
-        <v>632.7342807231195</v>
+        <v>632.7343419902274</v>
       </c>
       <c r="G5" t="n">
         <v>8820100</v>
@@ -587,16 +587,16 @@
         <v>46031</v>
       </c>
       <c r="C7" t="n">
-        <v>634.4539184570312</v>
+        <v>634.453857421875</v>
       </c>
       <c r="D7" t="n">
-        <v>635.5770968946526</v>
+        <v>635.5770357514454</v>
       </c>
       <c r="E7" t="n">
-        <v>629.9711540024175</v>
+        <v>629.9710933985081</v>
       </c>
       <c r="F7" t="n">
-        <v>631.313034949903</v>
+        <v>631.3129742169032</v>
       </c>
       <c r="G7" t="n">
         <v>7864100</v>
@@ -610,16 +610,16 @@
         <v>46034</v>
       </c>
       <c r="C8" t="n">
-        <v>635.4777221679688</v>
+        <v>635.4776611328125</v>
       </c>
       <c r="D8" t="n">
-        <v>636.2927150953415</v>
+        <v>636.2926539819083</v>
       </c>
       <c r="E8" t="n">
-        <v>631.3229204987674</v>
+        <v>631.3228598626637</v>
       </c>
       <c r="F8" t="n">
-        <v>631.3527683862371</v>
+        <v>631.3527077472665</v>
       </c>
       <c r="G8" t="n">
         <v>7929800</v>
@@ -679,16 +679,16 @@
         <v>46037</v>
       </c>
       <c r="C11" t="n">
-        <v>632.7741088867188</v>
+        <v>632.7740478515625</v>
       </c>
       <c r="D11" t="n">
-        <v>635.716249065159</v>
+        <v>635.7161877462142</v>
       </c>
       <c r="E11" t="n">
-        <v>631.8596836870233</v>
+        <v>631.8596227400693</v>
       </c>
       <c r="F11" t="n">
-        <v>634.9111447843152</v>
+        <v>634.911083543028</v>
       </c>
       <c r="G11" t="n">
         <v>6937000</v>
@@ -863,16 +863,16 @@
         <v>46050</v>
       </c>
       <c r="C19" t="n">
-        <v>635.7360229492188</v>
+        <v>635.736083984375</v>
       </c>
       <c r="D19" t="n">
-        <v>637.9326937327655</v>
+        <v>637.9327549788177</v>
       </c>
       <c r="E19" t="n">
-        <v>634.3643549546319</v>
+        <v>634.3644158580984</v>
       </c>
       <c r="F19" t="n">
-        <v>637.1772753396389</v>
+        <v>637.1773365131655</v>
       </c>
       <c r="G19" t="n">
         <v>5568700</v>
@@ -1001,16 +1001,16 @@
         <v>46058</v>
       </c>
       <c r="C25" t="n">
-        <v>619.3357543945312</v>
+        <v>619.335693359375</v>
       </c>
       <c r="D25" t="n">
-        <v>624.9516463379395</v>
+        <v>624.9515847493406</v>
       </c>
       <c r="E25" t="n">
-        <v>617.7454444517366</v>
+        <v>617.7453835733044</v>
       </c>
       <c r="F25" t="n">
-        <v>622.4567998403622</v>
+        <v>622.456738497629</v>
       </c>
       <c r="G25" t="n">
         <v>11714700</v>
@@ -1070,16 +1070,16 @@
         <v>46063</v>
       </c>
       <c r="C28" t="n">
-        <v>632.5951538085938</v>
+        <v>632.59521484375</v>
       </c>
       <c r="D28" t="n">
-        <v>636.7498943960981</v>
+        <v>636.7499558321192</v>
       </c>
       <c r="E28" t="n">
-        <v>632.237343193348</v>
+        <v>632.2374041939814</v>
       </c>
       <c r="F28" t="n">
-        <v>635.2788547558001</v>
+        <v>635.2789160498899</v>
       </c>
       <c r="G28" t="n">
         <v>13645300</v>
@@ -1116,16 +1116,16 @@
         <v>46065</v>
       </c>
       <c r="C30" t="n">
-        <v>622.7052612304688</v>
+        <v>622.705322265625</v>
       </c>
       <c r="D30" t="n">
-        <v>635.6565739786832</v>
+        <v>635.656636283277</v>
       </c>
       <c r="E30" t="n">
-        <v>621.9796906937136</v>
+        <v>621.9797516577522</v>
       </c>
       <c r="F30" t="n">
-        <v>634.6526658480624</v>
+        <v>634.652728054257</v>
       </c>
       <c r="G30" t="n">
         <v>8951100</v>
@@ -1300,16 +1300,16 @@
         <v>46078</v>
       </c>
       <c r="C38" t="n">
-        <v>633.6786499023438</v>
+        <v>633.6785888671875</v>
       </c>
       <c r="D38" t="n">
-        <v>634.1457814678613</v>
+        <v>634.1457203877115</v>
       </c>
       <c r="E38" t="n">
-        <v>630.9054657305335</v>
+        <v>630.9054049624871</v>
       </c>
       <c r="F38" t="n">
-        <v>630.935313617577</v>
+        <v>630.9352528466555</v>
       </c>
       <c r="G38" t="n">
         <v>12135200</v>
@@ -1346,16 +1346,16 @@
         <v>46080</v>
       </c>
       <c r="C40" t="n">
-        <v>627.2277221679688</v>
+        <v>627.227783203125</v>
       </c>
       <c r="D40" t="n">
-        <v>627.8738196368811</v>
+        <v>627.8738807349088</v>
       </c>
       <c r="E40" t="n">
-        <v>623.1525154659292</v>
+        <v>623.1525761045295</v>
       </c>
       <c r="F40" t="n">
-        <v>624.444649737325</v>
+        <v>624.4447105016621</v>
       </c>
       <c r="G40" t="n">
         <v>10471100</v>
@@ -1438,16 +1438,16 @@
         <v>46086</v>
       </c>
       <c r="C44" t="n">
-        <v>623.0233764648438</v>
+        <v>623.0233154296875</v>
       </c>
       <c r="D44" t="n">
-        <v>626.6910872371077</v>
+        <v>626.6910258426402</v>
       </c>
       <c r="E44" t="n">
-        <v>617.6460855023222</v>
+        <v>617.646024993958</v>
       </c>
       <c r="F44" t="n">
-        <v>623.5004573241831</v>
+        <v>623.5003962422892</v>
       </c>
       <c r="G44" t="n">
         <v>12198800</v>
@@ -1484,16 +1484,16 @@
         <v>46090</v>
       </c>
       <c r="C46" t="n">
-        <v>620.0315551757812</v>
+        <v>620.031494140625</v>
       </c>
       <c r="D46" t="n">
-        <v>621.5423921304164</v>
+        <v>621.542330946535</v>
       </c>
       <c r="E46" t="n">
-        <v>605.5197793738849</v>
+        <v>605.5197197672502</v>
       </c>
       <c r="F46" t="n">
-        <v>609.1576422868583</v>
+        <v>609.1575823221168</v>
       </c>
       <c r="G46" t="n">
         <v>13929200</v>
@@ -1530,16 +1530,16 @@
         <v>46092</v>
       </c>
       <c r="C48" t="n">
-        <v>618.2722778320312</v>
+        <v>618.272216796875</v>
       </c>
       <c r="D48" t="n">
-        <v>621.651701660167</v>
+        <v>621.6516402913978</v>
       </c>
       <c r="E48" t="n">
-        <v>615.5587288075508</v>
+        <v>615.5586680402731</v>
       </c>
       <c r="F48" t="n">
-        <v>619.4351927474164</v>
+        <v>619.4351315974586</v>
       </c>
       <c r="G48" t="n">
         <v>6433300</v>
@@ -1553,16 +1553,16 @@
         <v>46093</v>
       </c>
       <c r="C49" t="n">
-        <v>608.7997436523438</v>
+        <v>608.7998046875</v>
       </c>
       <c r="D49" t="n">
-        <v>613.9782906586722</v>
+        <v>613.9783522130032</v>
       </c>
       <c r="E49" t="n">
-        <v>608.720209964532</v>
+        <v>608.7202709917146</v>
       </c>
       <c r="F49" t="n">
-        <v>613.4911999039504</v>
+        <v>613.491261409448</v>
       </c>
       <c r="G49" t="n">
         <v>15487600</v>
@@ -1599,16 +1599,16 @@
         <v>46097</v>
       </c>
       <c r="C51" t="n">
-        <v>611.4735107421875</v>
+        <v>611.4735717773438</v>
       </c>
       <c r="D51" t="n">
-        <v>614.3460662066185</v>
+        <v>614.3461275285033</v>
       </c>
       <c r="E51" t="n">
-        <v>609.8334544713231</v>
+        <v>609.8335153427746</v>
       </c>
       <c r="F51" t="n">
-        <v>611.0063185641181</v>
+        <v>611.006379552641</v>
       </c>
       <c r="G51" t="n">
         <v>8303200</v>
@@ -1622,16 +1622,16 @@
         <v>46098</v>
       </c>
       <c r="C52" t="n">
-        <v>613.163330078125</v>
+        <v>613.1632690429688</v>
       </c>
       <c r="D52" t="n">
-        <v>616.5229160665718</v>
+        <v>616.5228546969976</v>
       </c>
       <c r="E52" t="n">
-        <v>612.5470804036939</v>
+        <v>612.5470194298802</v>
       </c>
       <c r="F52" t="n">
-        <v>614.6343698601297</v>
+        <v>614.6343086785441</v>
       </c>
       <c r="G52" t="n">
         <v>9941800</v>
@@ -1714,16 +1714,16 @@
         <v>46104</v>
       </c>
       <c r="C56" t="n">
-        <v>600.7785034179688</v>
+        <v>600.778564453125</v>
       </c>
       <c r="D56" t="n">
-        <v>607.3386678237272</v>
+        <v>607.3387295253531</v>
       </c>
       <c r="E56" t="n">
-        <v>599.4167847306644</v>
+        <v>599.416845627479</v>
       </c>
       <c r="F56" t="n">
-        <v>603.193815994715</v>
+        <v>603.1938772752512</v>
       </c>
       <c r="G56" t="n">
         <v>24014300</v>
@@ -1737,16 +1737,16 @@
         <v>46105</v>
       </c>
       <c r="C57" t="n">
-        <v>598.740966796875</v>
+        <v>598.7409057617188</v>
       </c>
       <c r="D57" t="n">
-        <v>602.2496101659307</v>
+        <v>602.2495487731062</v>
       </c>
       <c r="E57" t="n">
-        <v>595.6994549907438</v>
+        <v>595.6993942656367</v>
       </c>
       <c r="F57" t="n">
-        <v>597.0015387225677</v>
+        <v>597.0014778647273</v>
       </c>
       <c r="G57" t="n">
         <v>18363300</v>
@@ -1760,16 +1760,16 @@
         <v>46106</v>
       </c>
       <c r="C58" t="n">
-        <v>602.0010986328125</v>
+        <v>602.0010375976562</v>
       </c>
       <c r="D58" t="n">
-        <v>605.7582922570971</v>
+        <v>605.7582308410098</v>
       </c>
       <c r="E58" t="n">
-        <v>599.7150053798267</v>
+        <v>599.7149445764509</v>
       </c>
       <c r="F58" t="n">
-        <v>603.730638015276</v>
+        <v>603.7305768047668</v>
       </c>
       <c r="G58" t="n">
         <v>23288300</v>
@@ -3451,7 +3451,122 @@
         <v>691.25</v>
       </c>
       <c r="G131" t="n">
-        <v>5318000</v>
+        <v>5326400</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="C132" t="n">
+        <v>688.5</v>
+      </c>
+      <c r="D132" t="n">
+        <v>692.9600219726562</v>
+      </c>
+      <c r="E132" t="n">
+        <v>687.5399780273438</v>
+      </c>
+      <c r="F132" t="n">
+        <v>691.5999755859375</v>
+      </c>
+      <c r="G132" t="n">
+        <v>6637600</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C133" t="n">
+        <v>691.0999755859375</v>
+      </c>
+      <c r="D133" t="n">
+        <v>692.4000244140625</v>
+      </c>
+      <c r="E133" t="n">
+        <v>688.2000122070312</v>
+      </c>
+      <c r="F133" t="n">
+        <v>690.2100219726562</v>
+      </c>
+      <c r="G133" t="n">
+        <v>4610200</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C134" t="n">
+        <v>693.7999877929688</v>
+      </c>
+      <c r="D134" t="n">
+        <v>694.5</v>
+      </c>
+      <c r="E134" t="n">
+        <v>689.5800170898438</v>
+      </c>
+      <c r="F134" t="n">
+        <v>693.27001953125</v>
+      </c>
+      <c r="G134" t="n">
+        <v>4132800</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C135" t="n">
+        <v>690.1400146484375</v>
+      </c>
+      <c r="D135" t="n">
+        <v>693.5499877929688</v>
+      </c>
+      <c r="E135" t="n">
+        <v>687.4299926757812</v>
+      </c>
+      <c r="F135" t="n">
+        <v>691.97998046875</v>
+      </c>
+      <c r="G135" t="n">
+        <v>4764000</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C136" t="n">
+        <v>683.1699829101562</v>
+      </c>
+      <c r="D136" t="n">
+        <v>686.8699951171875</v>
+      </c>
+      <c r="E136" t="n">
+        <v>680.9199829101562</v>
+      </c>
+      <c r="F136" t="n">
+        <v>682.1199951171875</v>
+      </c>
+      <c r="G136" t="n">
+        <v>5646100</v>
       </c>
     </row>
   </sheetData>

--- a/Data/voo.xlsx
+++ b/Data/voo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,16 +495,16 @@
         <v>46027</v>
       </c>
       <c r="C3" t="n">
-        <v>628.6392822265625</v>
+        <v>628.6392211914062</v>
       </c>
       <c r="D3" t="n">
-        <v>630.2096936449323</v>
+        <v>630.2096324573033</v>
       </c>
       <c r="E3" t="n">
-        <v>627.4166714981994</v>
+        <v>627.4166105817476</v>
       </c>
       <c r="F3" t="n">
-        <v>627.5657896032119</v>
+        <v>627.565728672282</v>
       </c>
       <c r="G3" t="n">
         <v>16175600</v>
@@ -541,16 +541,16 @@
         <v>46029</v>
       </c>
       <c r="C5" t="n">
-        <v>630.3388671875</v>
+        <v>630.3388061523438</v>
       </c>
       <c r="D5" t="n">
-        <v>634.364388398435</v>
+        <v>634.3643269734911</v>
       </c>
       <c r="E5" t="n">
-        <v>630.1003267700273</v>
+        <v>630.1002657579688</v>
       </c>
       <c r="F5" t="n">
-        <v>632.7343419902274</v>
+        <v>632.7342807231195</v>
       </c>
       <c r="G5" t="n">
         <v>8820100</v>
@@ -587,16 +587,16 @@
         <v>46031</v>
       </c>
       <c r="C7" t="n">
-        <v>634.453857421875</v>
+        <v>634.4539184570312</v>
       </c>
       <c r="D7" t="n">
-        <v>635.5770357514454</v>
+        <v>635.5770968946526</v>
       </c>
       <c r="E7" t="n">
-        <v>629.9710933985081</v>
+        <v>629.9711540024175</v>
       </c>
       <c r="F7" t="n">
-        <v>631.3129742169032</v>
+        <v>631.313034949903</v>
       </c>
       <c r="G7" t="n">
         <v>7864100</v>
@@ -610,16 +610,16 @@
         <v>46034</v>
       </c>
       <c r="C8" t="n">
-        <v>635.4776611328125</v>
+        <v>635.4777221679688</v>
       </c>
       <c r="D8" t="n">
-        <v>636.2926539819083</v>
+        <v>636.2927150953415</v>
       </c>
       <c r="E8" t="n">
-        <v>631.3228598626637</v>
+        <v>631.3229204987674</v>
       </c>
       <c r="F8" t="n">
-        <v>631.3527077472665</v>
+        <v>631.3527683862371</v>
       </c>
       <c r="G8" t="n">
         <v>7929800</v>
@@ -679,16 +679,16 @@
         <v>46037</v>
       </c>
       <c r="C11" t="n">
-        <v>632.7740478515625</v>
+        <v>632.7741088867188</v>
       </c>
       <c r="D11" t="n">
-        <v>635.7161877462142</v>
+        <v>635.716249065159</v>
       </c>
       <c r="E11" t="n">
-        <v>631.8596227400693</v>
+        <v>631.8596836870233</v>
       </c>
       <c r="F11" t="n">
-        <v>634.911083543028</v>
+        <v>634.9111447843152</v>
       </c>
       <c r="G11" t="n">
         <v>6937000</v>
@@ -863,16 +863,16 @@
         <v>46050</v>
       </c>
       <c r="C19" t="n">
-        <v>635.736083984375</v>
+        <v>635.7360229492188</v>
       </c>
       <c r="D19" t="n">
-        <v>637.9327549788177</v>
+        <v>637.9326937327655</v>
       </c>
       <c r="E19" t="n">
-        <v>634.3644158580984</v>
+        <v>634.3643549546319</v>
       </c>
       <c r="F19" t="n">
-        <v>637.1773365131655</v>
+        <v>637.1772753396389</v>
       </c>
       <c r="G19" t="n">
         <v>5568700</v>
@@ -1001,16 +1001,16 @@
         <v>46058</v>
       </c>
       <c r="C25" t="n">
-        <v>619.335693359375</v>
+        <v>619.3357543945312</v>
       </c>
       <c r="D25" t="n">
-        <v>624.9515847493406</v>
+        <v>624.9516463379395</v>
       </c>
       <c r="E25" t="n">
-        <v>617.7453835733044</v>
+        <v>617.7454444517366</v>
       </c>
       <c r="F25" t="n">
-        <v>622.456738497629</v>
+        <v>622.4567998403622</v>
       </c>
       <c r="G25" t="n">
         <v>11714700</v>
@@ -1070,16 +1070,16 @@
         <v>46063</v>
       </c>
       <c r="C28" t="n">
-        <v>632.59521484375</v>
+        <v>632.5951538085938</v>
       </c>
       <c r="D28" t="n">
-        <v>636.7499558321192</v>
+        <v>636.7498943960981</v>
       </c>
       <c r="E28" t="n">
-        <v>632.2374041939814</v>
+        <v>632.237343193348</v>
       </c>
       <c r="F28" t="n">
-        <v>635.2789160498899</v>
+        <v>635.2788547558001</v>
       </c>
       <c r="G28" t="n">
         <v>13645300</v>
@@ -1116,16 +1116,16 @@
         <v>46065</v>
       </c>
       <c r="C30" t="n">
-        <v>622.705322265625</v>
+        <v>622.7052612304688</v>
       </c>
       <c r="D30" t="n">
-        <v>635.656636283277</v>
+        <v>635.6565739786832</v>
       </c>
       <c r="E30" t="n">
-        <v>621.9797516577522</v>
+        <v>621.9796906937136</v>
       </c>
       <c r="F30" t="n">
-        <v>634.652728054257</v>
+        <v>634.6526658480624</v>
       </c>
       <c r="G30" t="n">
         <v>8951100</v>
@@ -1300,16 +1300,16 @@
         <v>46078</v>
       </c>
       <c r="C38" t="n">
-        <v>633.6785888671875</v>
+        <v>633.6786499023438</v>
       </c>
       <c r="D38" t="n">
-        <v>634.1457203877115</v>
+        <v>634.1457814678613</v>
       </c>
       <c r="E38" t="n">
-        <v>630.9054049624871</v>
+        <v>630.9054657305335</v>
       </c>
       <c r="F38" t="n">
-        <v>630.9352528466555</v>
+        <v>630.935313617577</v>
       </c>
       <c r="G38" t="n">
         <v>12135200</v>
@@ -1346,16 +1346,16 @@
         <v>46080</v>
       </c>
       <c r="C40" t="n">
-        <v>627.227783203125</v>
+        <v>627.2277221679688</v>
       </c>
       <c r="D40" t="n">
-        <v>627.8738807349088</v>
+        <v>627.8738196368811</v>
       </c>
       <c r="E40" t="n">
-        <v>623.1525761045295</v>
+        <v>623.1525154659292</v>
       </c>
       <c r="F40" t="n">
-        <v>624.4447105016621</v>
+        <v>624.444649737325</v>
       </c>
       <c r="G40" t="n">
         <v>10471100</v>
@@ -1438,16 +1438,16 @@
         <v>46086</v>
       </c>
       <c r="C44" t="n">
-        <v>623.0233154296875</v>
+        <v>623.0233764648438</v>
       </c>
       <c r="D44" t="n">
-        <v>626.6910258426402</v>
+        <v>626.6910872371077</v>
       </c>
       <c r="E44" t="n">
-        <v>617.646024993958</v>
+        <v>617.6460855023222</v>
       </c>
       <c r="F44" t="n">
-        <v>623.5003962422892</v>
+        <v>623.5004573241831</v>
       </c>
       <c r="G44" t="n">
         <v>12198800</v>
@@ -1484,16 +1484,16 @@
         <v>46090</v>
       </c>
       <c r="C46" t="n">
-        <v>620.031494140625</v>
+        <v>620.0315551757812</v>
       </c>
       <c r="D46" t="n">
-        <v>621.542330946535</v>
+        <v>621.5423921304164</v>
       </c>
       <c r="E46" t="n">
-        <v>605.5197197672502</v>
+        <v>605.5197793738849</v>
       </c>
       <c r="F46" t="n">
-        <v>609.1575823221168</v>
+        <v>609.1576422868583</v>
       </c>
       <c r="G46" t="n">
         <v>13929200</v>
@@ -1530,16 +1530,16 @@
         <v>46092</v>
       </c>
       <c r="C48" t="n">
-        <v>618.272216796875</v>
+        <v>618.2722778320312</v>
       </c>
       <c r="D48" t="n">
-        <v>621.6516402913978</v>
+        <v>621.651701660167</v>
       </c>
       <c r="E48" t="n">
-        <v>615.5586680402731</v>
+        <v>615.5587288075508</v>
       </c>
       <c r="F48" t="n">
-        <v>619.4351315974586</v>
+        <v>619.4351927474164</v>
       </c>
       <c r="G48" t="n">
         <v>6433300</v>
@@ -1553,16 +1553,16 @@
         <v>46093</v>
       </c>
       <c r="C49" t="n">
-        <v>608.7998046875</v>
+        <v>608.7997436523438</v>
       </c>
       <c r="D49" t="n">
-        <v>613.9783522130032</v>
+        <v>613.9782906586722</v>
       </c>
       <c r="E49" t="n">
-        <v>608.7202709917146</v>
+        <v>608.720209964532</v>
       </c>
       <c r="F49" t="n">
-        <v>613.491261409448</v>
+        <v>613.4911999039504</v>
       </c>
       <c r="G49" t="n">
         <v>15487600</v>
@@ -1599,16 +1599,16 @@
         <v>46097</v>
       </c>
       <c r="C51" t="n">
-        <v>611.4735717773438</v>
+        <v>611.4735107421875</v>
       </c>
       <c r="D51" t="n">
-        <v>614.3461275285033</v>
+        <v>614.3460662066185</v>
       </c>
       <c r="E51" t="n">
-        <v>609.8335153427746</v>
+        <v>609.8334544713231</v>
       </c>
       <c r="F51" t="n">
-        <v>611.006379552641</v>
+        <v>611.0063185641181</v>
       </c>
       <c r="G51" t="n">
         <v>8303200</v>
@@ -1622,16 +1622,16 @@
         <v>46098</v>
       </c>
       <c r="C52" t="n">
-        <v>613.1632690429688</v>
+        <v>613.163330078125</v>
       </c>
       <c r="D52" t="n">
-        <v>616.5228546969976</v>
+        <v>616.5229160665718</v>
       </c>
       <c r="E52" t="n">
-        <v>612.5470194298802</v>
+        <v>612.5470804036939</v>
       </c>
       <c r="F52" t="n">
-        <v>614.6343086785441</v>
+        <v>614.6343698601297</v>
       </c>
       <c r="G52" t="n">
         <v>9941800</v>
@@ -1714,16 +1714,16 @@
         <v>46104</v>
       </c>
       <c r="C56" t="n">
-        <v>600.778564453125</v>
+        <v>600.7785034179688</v>
       </c>
       <c r="D56" t="n">
-        <v>607.3387295253531</v>
+        <v>607.3386678237272</v>
       </c>
       <c r="E56" t="n">
-        <v>599.416845627479</v>
+        <v>599.4167847306644</v>
       </c>
       <c r="F56" t="n">
-        <v>603.1938772752512</v>
+        <v>603.193815994715</v>
       </c>
       <c r="G56" t="n">
         <v>24014300</v>
@@ -1737,16 +1737,16 @@
         <v>46105</v>
       </c>
       <c r="C57" t="n">
-        <v>598.7409057617188</v>
+        <v>598.740966796875</v>
       </c>
       <c r="D57" t="n">
-        <v>602.2495487731062</v>
+        <v>602.2496101659307</v>
       </c>
       <c r="E57" t="n">
-        <v>595.6993942656367</v>
+        <v>595.6994549907438</v>
       </c>
       <c r="F57" t="n">
-        <v>597.0014778647273</v>
+        <v>597.0015387225677</v>
       </c>
       <c r="G57" t="n">
         <v>18363300</v>
@@ -1760,16 +1760,16 @@
         <v>46106</v>
       </c>
       <c r="C58" t="n">
-        <v>602.0010375976562</v>
+        <v>602.0010986328125</v>
       </c>
       <c r="D58" t="n">
-        <v>605.7582308410098</v>
+        <v>605.7582922570971</v>
       </c>
       <c r="E58" t="n">
-        <v>599.7149445764509</v>
+        <v>599.7150053798267</v>
       </c>
       <c r="F58" t="n">
-        <v>603.7305768047668</v>
+        <v>603.730638015276</v>
       </c>
       <c r="G58" t="n">
         <v>23288300</v>
@@ -3566,7 +3566,191 @@
         <v>682.1199951171875</v>
       </c>
       <c r="G136" t="n">
-        <v>5646100</v>
+        <v>5679300</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C137" t="n">
+        <v>682.2100219726562</v>
+      </c>
+      <c r="D137" t="n">
+        <v>688.2000122070312</v>
+      </c>
+      <c r="E137" t="n">
+        <v>681.5700073242188</v>
+      </c>
+      <c r="F137" t="n">
+        <v>686.6699829101562</v>
+      </c>
+      <c r="G137" t="n">
+        <v>5360300</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C138" t="n">
+        <v>687.8699951171875</v>
+      </c>
+      <c r="D138" t="n">
+        <v>688.489990234375</v>
+      </c>
+      <c r="E138" t="n">
+        <v>684.030029296875</v>
+      </c>
+      <c r="F138" t="n">
+        <v>685.9500122070312</v>
+      </c>
+      <c r="G138" t="n">
+        <v>4075500</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C139" t="n">
+        <v>687.030029296875</v>
+      </c>
+      <c r="D139" t="n">
+        <v>689.4000244140625</v>
+      </c>
+      <c r="E139" t="n">
+        <v>686.02001953125</v>
+      </c>
+      <c r="F139" t="n">
+        <v>686.2899780273438</v>
+      </c>
+      <c r="G139" t="n">
+        <v>3418300</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C140" t="n">
+        <v>678.6099853515625</v>
+      </c>
+      <c r="D140" t="n">
+        <v>682.5499877929688</v>
+      </c>
+      <c r="E140" t="n">
+        <v>675.760009765625</v>
+      </c>
+      <c r="F140" t="n">
+        <v>679.5499877929688</v>
+      </c>
+      <c r="G140" t="n">
+        <v>4983100</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C141" t="n">
+        <v>679.1400146484375</v>
+      </c>
+      <c r="D141" t="n">
+        <v>683.5499877929688</v>
+      </c>
+      <c r="E141" t="n">
+        <v>677.7000122070312</v>
+      </c>
+      <c r="F141" t="n">
+        <v>678.7999877929688</v>
+      </c>
+      <c r="G141" t="n">
+        <v>6311600</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C142" t="n">
+        <v>679.3099975585938</v>
+      </c>
+      <c r="D142" t="n">
+        <v>685.239990234375</v>
+      </c>
+      <c r="E142" t="n">
+        <v>676.4000244140625</v>
+      </c>
+      <c r="F142" t="n">
+        <v>684.6900024414062</v>
+      </c>
+      <c r="G142" t="n">
+        <v>5232200</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C143" t="n">
+        <v>680.9600219726562</v>
+      </c>
+      <c r="D143" t="n">
+        <v>682.760009765625</v>
+      </c>
+      <c r="E143" t="n">
+        <v>676.47998046875</v>
+      </c>
+      <c r="F143" t="n">
+        <v>679.4500122070312</v>
+      </c>
+      <c r="G143" t="n">
+        <v>5090000</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C144" t="n">
+        <v>670.6300048828125</v>
+      </c>
+      <c r="D144" t="n">
+        <v>682.6209716796875</v>
+      </c>
+      <c r="E144" t="n">
+        <v>670.155029296875</v>
+      </c>
+      <c r="F144" t="n">
+        <v>680.1199951171875</v>
+      </c>
+      <c r="G144" t="n">
+        <v>6578285</v>
       </c>
     </row>
   </sheetData>

--- a/Data/voo.xlsx
+++ b/Data/voo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,16 +495,16 @@
         <v>46027</v>
       </c>
       <c r="C3" t="n">
-        <v>628.6392211914062</v>
+        <v>628.6392822265625</v>
       </c>
       <c r="D3" t="n">
-        <v>630.2096324573033</v>
+        <v>630.2096936449323</v>
       </c>
       <c r="E3" t="n">
-        <v>627.4166105817476</v>
+        <v>627.4166714981994</v>
       </c>
       <c r="F3" t="n">
-        <v>627.565728672282</v>
+        <v>627.5657896032119</v>
       </c>
       <c r="G3" t="n">
         <v>16175600</v>
@@ -541,16 +541,16 @@
         <v>46029</v>
       </c>
       <c r="C5" t="n">
-        <v>630.3388061523438</v>
+        <v>630.3388671875</v>
       </c>
       <c r="D5" t="n">
-        <v>634.3643269734911</v>
+        <v>634.364388398435</v>
       </c>
       <c r="E5" t="n">
-        <v>630.1002657579688</v>
+        <v>630.1003267700273</v>
       </c>
       <c r="F5" t="n">
-        <v>632.7342807231195</v>
+        <v>632.7343419902274</v>
       </c>
       <c r="G5" t="n">
         <v>8820100</v>
@@ -587,16 +587,16 @@
         <v>46031</v>
       </c>
       <c r="C7" t="n">
-        <v>634.4539184570312</v>
+        <v>634.453857421875</v>
       </c>
       <c r="D7" t="n">
-        <v>635.5770968946526</v>
+        <v>635.5770357514454</v>
       </c>
       <c r="E7" t="n">
-        <v>629.9711540024175</v>
+        <v>629.9710933985081</v>
       </c>
       <c r="F7" t="n">
-        <v>631.313034949903</v>
+        <v>631.3129742169032</v>
       </c>
       <c r="G7" t="n">
         <v>7864100</v>
@@ -610,16 +610,16 @@
         <v>46034</v>
       </c>
       <c r="C8" t="n">
-        <v>635.4777221679688</v>
+        <v>635.4776611328125</v>
       </c>
       <c r="D8" t="n">
-        <v>636.2927150953415</v>
+        <v>636.2926539819083</v>
       </c>
       <c r="E8" t="n">
-        <v>631.3229204987674</v>
+        <v>631.3228598626637</v>
       </c>
       <c r="F8" t="n">
-        <v>631.3527683862371</v>
+        <v>631.3527077472665</v>
       </c>
       <c r="G8" t="n">
         <v>7929800</v>
@@ -679,16 +679,16 @@
         <v>46037</v>
       </c>
       <c r="C11" t="n">
-        <v>632.7741088867188</v>
+        <v>632.7740478515625</v>
       </c>
       <c r="D11" t="n">
-        <v>635.716249065159</v>
+        <v>635.7161877462142</v>
       </c>
       <c r="E11" t="n">
-        <v>631.8596836870233</v>
+        <v>631.8596227400693</v>
       </c>
       <c r="F11" t="n">
-        <v>634.9111447843152</v>
+        <v>634.911083543028</v>
       </c>
       <c r="G11" t="n">
         <v>6937000</v>
@@ -863,16 +863,16 @@
         <v>46050</v>
       </c>
       <c r="C19" t="n">
-        <v>635.7360229492188</v>
+        <v>635.736083984375</v>
       </c>
       <c r="D19" t="n">
-        <v>637.9326937327655</v>
+        <v>637.9327549788177</v>
       </c>
       <c r="E19" t="n">
-        <v>634.3643549546319</v>
+        <v>634.3644158580984</v>
       </c>
       <c r="F19" t="n">
-        <v>637.1772753396389</v>
+        <v>637.1773365131655</v>
       </c>
       <c r="G19" t="n">
         <v>5568700</v>
@@ -1001,16 +1001,16 @@
         <v>46058</v>
       </c>
       <c r="C25" t="n">
-        <v>619.3357543945312</v>
+        <v>619.335693359375</v>
       </c>
       <c r="D25" t="n">
-        <v>624.9516463379395</v>
+        <v>624.9515847493406</v>
       </c>
       <c r="E25" t="n">
-        <v>617.7454444517366</v>
+        <v>617.7453835733044</v>
       </c>
       <c r="F25" t="n">
-        <v>622.4567998403622</v>
+        <v>622.456738497629</v>
       </c>
       <c r="G25" t="n">
         <v>11714700</v>
@@ -1070,16 +1070,16 @@
         <v>46063</v>
       </c>
       <c r="C28" t="n">
-        <v>632.5951538085938</v>
+        <v>632.59521484375</v>
       </c>
       <c r="D28" t="n">
-        <v>636.7498943960981</v>
+        <v>636.7499558321192</v>
       </c>
       <c r="E28" t="n">
-        <v>632.237343193348</v>
+        <v>632.2374041939814</v>
       </c>
       <c r="F28" t="n">
-        <v>635.2788547558001</v>
+        <v>635.2789160498899</v>
       </c>
       <c r="G28" t="n">
         <v>13645300</v>
@@ -1116,16 +1116,16 @@
         <v>46065</v>
       </c>
       <c r="C30" t="n">
-        <v>622.7052612304688</v>
+        <v>622.705322265625</v>
       </c>
       <c r="D30" t="n">
-        <v>635.6565739786832</v>
+        <v>635.656636283277</v>
       </c>
       <c r="E30" t="n">
-        <v>621.9796906937136</v>
+        <v>621.9797516577522</v>
       </c>
       <c r="F30" t="n">
-        <v>634.6526658480624</v>
+        <v>634.652728054257</v>
       </c>
       <c r="G30" t="n">
         <v>8951100</v>
@@ -1300,16 +1300,16 @@
         <v>46078</v>
       </c>
       <c r="C38" t="n">
-        <v>633.6786499023438</v>
+        <v>633.6785888671875</v>
       </c>
       <c r="D38" t="n">
-        <v>634.1457814678613</v>
+        <v>634.1457203877115</v>
       </c>
       <c r="E38" t="n">
-        <v>630.9054657305335</v>
+        <v>630.9054049624871</v>
       </c>
       <c r="F38" t="n">
-        <v>630.935313617577</v>
+        <v>630.9352528466555</v>
       </c>
       <c r="G38" t="n">
         <v>12135200</v>
@@ -1346,16 +1346,16 @@
         <v>46080</v>
       </c>
       <c r="C40" t="n">
-        <v>627.2277221679688</v>
+        <v>627.227783203125</v>
       </c>
       <c r="D40" t="n">
-        <v>627.8738196368811</v>
+        <v>627.8738807349088</v>
       </c>
       <c r="E40" t="n">
-        <v>623.1525154659292</v>
+        <v>623.1525761045295</v>
       </c>
       <c r="F40" t="n">
-        <v>624.444649737325</v>
+        <v>624.4447105016621</v>
       </c>
       <c r="G40" t="n">
         <v>10471100</v>
@@ -1438,16 +1438,16 @@
         <v>46086</v>
       </c>
       <c r="C44" t="n">
-        <v>623.0233764648438</v>
+        <v>623.0233154296875</v>
       </c>
       <c r="D44" t="n">
-        <v>626.6910872371077</v>
+        <v>626.6910258426402</v>
       </c>
       <c r="E44" t="n">
-        <v>617.6460855023222</v>
+        <v>617.646024993958</v>
       </c>
       <c r="F44" t="n">
-        <v>623.5004573241831</v>
+        <v>623.5003962422892</v>
       </c>
       <c r="G44" t="n">
         <v>12198800</v>
@@ -1484,16 +1484,16 @@
         <v>46090</v>
       </c>
       <c r="C46" t="n">
-        <v>620.0315551757812</v>
+        <v>620.031494140625</v>
       </c>
       <c r="D46" t="n">
-        <v>621.5423921304164</v>
+        <v>621.542330946535</v>
       </c>
       <c r="E46" t="n">
-        <v>605.5197793738849</v>
+        <v>605.5197197672502</v>
       </c>
       <c r="F46" t="n">
-        <v>609.1576422868583</v>
+        <v>609.1575823221168</v>
       </c>
       <c r="G46" t="n">
         <v>13929200</v>
@@ -1530,16 +1530,16 @@
         <v>46092</v>
       </c>
       <c r="C48" t="n">
-        <v>618.2722778320312</v>
+        <v>618.272216796875</v>
       </c>
       <c r="D48" t="n">
-        <v>621.651701660167</v>
+        <v>621.6516402913978</v>
       </c>
       <c r="E48" t="n">
-        <v>615.5587288075508</v>
+        <v>615.5586680402731</v>
       </c>
       <c r="F48" t="n">
-        <v>619.4351927474164</v>
+        <v>619.4351315974586</v>
       </c>
       <c r="G48" t="n">
         <v>6433300</v>
@@ -1553,16 +1553,16 @@
         <v>46093</v>
       </c>
       <c r="C49" t="n">
-        <v>608.7997436523438</v>
+        <v>608.7998046875</v>
       </c>
       <c r="D49" t="n">
-        <v>613.9782906586722</v>
+        <v>613.9783522130032</v>
       </c>
       <c r="E49" t="n">
-        <v>608.720209964532</v>
+        <v>608.7202709917146</v>
       </c>
       <c r="F49" t="n">
-        <v>613.4911999039504</v>
+        <v>613.491261409448</v>
       </c>
       <c r="G49" t="n">
         <v>15487600</v>
@@ -1599,16 +1599,16 @@
         <v>46097</v>
       </c>
       <c r="C51" t="n">
-        <v>611.4735107421875</v>
+        <v>611.4735717773438</v>
       </c>
       <c r="D51" t="n">
-        <v>614.3460662066185</v>
+        <v>614.3461275285033</v>
       </c>
       <c r="E51" t="n">
-        <v>609.8334544713231</v>
+        <v>609.8335153427746</v>
       </c>
       <c r="F51" t="n">
-        <v>611.0063185641181</v>
+        <v>611.006379552641</v>
       </c>
       <c r="G51" t="n">
         <v>8303200</v>
@@ -1622,16 +1622,16 @@
         <v>46098</v>
       </c>
       <c r="C52" t="n">
-        <v>613.163330078125</v>
+        <v>613.1632690429688</v>
       </c>
       <c r="D52" t="n">
-        <v>616.5229160665718</v>
+        <v>616.5228546969976</v>
       </c>
       <c r="E52" t="n">
-        <v>612.5470804036939</v>
+        <v>612.5470194298802</v>
       </c>
       <c r="F52" t="n">
-        <v>614.6343698601297</v>
+        <v>614.6343086785441</v>
       </c>
       <c r="G52" t="n">
         <v>9941800</v>
@@ -1714,16 +1714,16 @@
         <v>46104</v>
       </c>
       <c r="C56" t="n">
-        <v>600.7785034179688</v>
+        <v>600.778564453125</v>
       </c>
       <c r="D56" t="n">
-        <v>607.3386678237272</v>
+        <v>607.3387295253531</v>
       </c>
       <c r="E56" t="n">
-        <v>599.4167847306644</v>
+        <v>599.416845627479</v>
       </c>
       <c r="F56" t="n">
-        <v>603.193815994715</v>
+        <v>603.1938772752512</v>
       </c>
       <c r="G56" t="n">
         <v>24014300</v>
@@ -1737,16 +1737,16 @@
         <v>46105</v>
       </c>
       <c r="C57" t="n">
-        <v>598.740966796875</v>
+        <v>598.7409057617188</v>
       </c>
       <c r="D57" t="n">
-        <v>602.2496101659307</v>
+        <v>602.2495487731062</v>
       </c>
       <c r="E57" t="n">
-        <v>595.6994549907438</v>
+        <v>595.6993942656367</v>
       </c>
       <c r="F57" t="n">
-        <v>597.0015387225677</v>
+        <v>597.0014778647273</v>
       </c>
       <c r="G57" t="n">
         <v>18363300</v>
@@ -1760,16 +1760,16 @@
         <v>46106</v>
       </c>
       <c r="C58" t="n">
-        <v>602.0010986328125</v>
+        <v>602.0010375976562</v>
       </c>
       <c r="D58" t="n">
-        <v>605.7582922570971</v>
+        <v>605.7582308410098</v>
       </c>
       <c r="E58" t="n">
-        <v>599.7150053798267</v>
+        <v>599.7149445764509</v>
       </c>
       <c r="F58" t="n">
-        <v>603.730638015276</v>
+        <v>603.7305768047668</v>
       </c>
       <c r="G58" t="n">
         <v>23288300</v>
@@ -3741,16 +3741,154 @@
         <v>670.6300048828125</v>
       </c>
       <c r="D144" t="n">
-        <v>682.6209716796875</v>
+        <v>682.6300048828125</v>
       </c>
       <c r="E144" t="n">
-        <v>670.155029296875</v>
+        <v>670.1599731445312</v>
       </c>
       <c r="F144" t="n">
         <v>680.1199951171875</v>
       </c>
       <c r="G144" t="n">
-        <v>6578285</v>
+        <v>7970700</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="C145" t="n">
+        <v>681.7899780273438</v>
+      </c>
+      <c r="D145" t="n">
+        <v>682.4400024414062</v>
+      </c>
+      <c r="E145" t="n">
+        <v>675.2100219726562</v>
+      </c>
+      <c r="F145" t="n">
+        <v>676.5399780273438</v>
+      </c>
+      <c r="G145" t="n">
+        <v>6094800</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C146" t="n">
+        <v>686.6500244140625</v>
+      </c>
+      <c r="D146" t="n">
+        <v>688.3499755859375</v>
+      </c>
+      <c r="E146" t="n">
+        <v>678.0599975585938</v>
+      </c>
+      <c r="F146" t="n">
+        <v>684.5</v>
+      </c>
+      <c r="G146" t="n">
+        <v>7715400</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="C147" t="n">
+        <v>696.4000244140625</v>
+      </c>
+      <c r="D147" t="n">
+        <v>697.3099975585938</v>
+      </c>
+      <c r="E147" t="n">
+        <v>688.6099853515625</v>
+      </c>
+      <c r="F147" t="n">
+        <v>688.8300170898438</v>
+      </c>
+      <c r="G147" t="n">
+        <v>7283200</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C148" t="n">
+        <v>708.97998046875</v>
+      </c>
+      <c r="D148" t="n">
+        <v>710.9099731445312</v>
+      </c>
+      <c r="E148" t="n">
+        <v>699.0700073242188</v>
+      </c>
+      <c r="F148" t="n">
+        <v>699.1599731445312</v>
+      </c>
+      <c r="G148" t="n">
+        <v>6566400</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C149" t="n">
+        <v>707.5999755859375</v>
+      </c>
+      <c r="D149" t="n">
+        <v>714.1599731445312</v>
+      </c>
+      <c r="E149" t="n">
+        <v>707.3200073242188</v>
+      </c>
+      <c r="F149" t="n">
+        <v>713.1400146484375</v>
+      </c>
+      <c r="G149" t="n">
+        <v>5225700</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C150" t="n">
+        <v>706.4000244140625</v>
+      </c>
+      <c r="D150" t="n">
+        <v>709.4619140625</v>
+      </c>
+      <c r="E150" t="n">
+        <v>705.4299926757812</v>
+      </c>
+      <c r="F150" t="n">
+        <v>707.9299926757812</v>
+      </c>
+      <c r="G150" t="n">
+        <v>4302202</v>
       </c>
     </row>
   </sheetData>

--- a/Data/voo.xlsx
+++ b/Data/voo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,16 +495,16 @@
         <v>46027</v>
       </c>
       <c r="C3" t="n">
-        <v>628.6392822265625</v>
+        <v>628.6392211914062</v>
       </c>
       <c r="D3" t="n">
-        <v>630.2096936449323</v>
+        <v>630.2096324573033</v>
       </c>
       <c r="E3" t="n">
-        <v>627.4166714981994</v>
+        <v>627.4166105817476</v>
       </c>
       <c r="F3" t="n">
-        <v>627.5657896032119</v>
+        <v>627.565728672282</v>
       </c>
       <c r="G3" t="n">
         <v>16175600</v>
@@ -541,16 +541,16 @@
         <v>46029</v>
       </c>
       <c r="C5" t="n">
-        <v>630.3388671875</v>
+        <v>630.3388061523438</v>
       </c>
       <c r="D5" t="n">
-        <v>634.364388398435</v>
+        <v>634.3643269734911</v>
       </c>
       <c r="E5" t="n">
-        <v>630.1003267700273</v>
+        <v>630.1002657579688</v>
       </c>
       <c r="F5" t="n">
-        <v>632.7343419902274</v>
+        <v>632.7342807231195</v>
       </c>
       <c r="G5" t="n">
         <v>8820100</v>
@@ -587,16 +587,16 @@
         <v>46031</v>
       </c>
       <c r="C7" t="n">
-        <v>634.453857421875</v>
+        <v>634.4539184570312</v>
       </c>
       <c r="D7" t="n">
-        <v>635.5770357514454</v>
+        <v>635.5770968946526</v>
       </c>
       <c r="E7" t="n">
-        <v>629.9710933985081</v>
+        <v>629.9711540024175</v>
       </c>
       <c r="F7" t="n">
-        <v>631.3129742169032</v>
+        <v>631.313034949903</v>
       </c>
       <c r="G7" t="n">
         <v>7864100</v>
@@ -610,16 +610,16 @@
         <v>46034</v>
       </c>
       <c r="C8" t="n">
-        <v>635.4776611328125</v>
+        <v>635.4777221679688</v>
       </c>
       <c r="D8" t="n">
-        <v>636.2926539819083</v>
+        <v>636.2927150953415</v>
       </c>
       <c r="E8" t="n">
-        <v>631.3228598626637</v>
+        <v>631.3229204987674</v>
       </c>
       <c r="F8" t="n">
-        <v>631.3527077472665</v>
+        <v>631.3527683862371</v>
       </c>
       <c r="G8" t="n">
         <v>7929800</v>
@@ -679,16 +679,16 @@
         <v>46037</v>
       </c>
       <c r="C11" t="n">
-        <v>632.7740478515625</v>
+        <v>632.7741088867188</v>
       </c>
       <c r="D11" t="n">
-        <v>635.7161877462142</v>
+        <v>635.716249065159</v>
       </c>
       <c r="E11" t="n">
-        <v>631.8596227400693</v>
+        <v>631.8596836870233</v>
       </c>
       <c r="F11" t="n">
-        <v>634.911083543028</v>
+        <v>634.9111447843152</v>
       </c>
       <c r="G11" t="n">
         <v>6937000</v>
@@ -863,16 +863,16 @@
         <v>46050</v>
       </c>
       <c r="C19" t="n">
-        <v>635.736083984375</v>
+        <v>635.7360229492188</v>
       </c>
       <c r="D19" t="n">
-        <v>637.9327549788177</v>
+        <v>637.9326937327655</v>
       </c>
       <c r="E19" t="n">
-        <v>634.3644158580984</v>
+        <v>634.3643549546319</v>
       </c>
       <c r="F19" t="n">
-        <v>637.1773365131655</v>
+        <v>637.1772753396389</v>
       </c>
       <c r="G19" t="n">
         <v>5568700</v>
@@ -1001,16 +1001,16 @@
         <v>46058</v>
       </c>
       <c r="C25" t="n">
-        <v>619.335693359375</v>
+        <v>619.3357543945312</v>
       </c>
       <c r="D25" t="n">
-        <v>624.9515847493406</v>
+        <v>624.9516463379395</v>
       </c>
       <c r="E25" t="n">
-        <v>617.7453835733044</v>
+        <v>617.7454444517366</v>
       </c>
       <c r="F25" t="n">
-        <v>622.456738497629</v>
+        <v>622.4567998403622</v>
       </c>
       <c r="G25" t="n">
         <v>11714700</v>
@@ -1070,16 +1070,16 @@
         <v>46063</v>
       </c>
       <c r="C28" t="n">
-        <v>632.59521484375</v>
+        <v>632.5951538085938</v>
       </c>
       <c r="D28" t="n">
-        <v>636.7499558321192</v>
+        <v>636.7498943960981</v>
       </c>
       <c r="E28" t="n">
-        <v>632.2374041939814</v>
+        <v>632.237343193348</v>
       </c>
       <c r="F28" t="n">
-        <v>635.2789160498899</v>
+        <v>635.2788547558001</v>
       </c>
       <c r="G28" t="n">
         <v>13645300</v>
@@ -1116,16 +1116,16 @@
         <v>46065</v>
       </c>
       <c r="C30" t="n">
-        <v>622.705322265625</v>
+        <v>622.7052612304688</v>
       </c>
       <c r="D30" t="n">
-        <v>635.656636283277</v>
+        <v>635.6565739786832</v>
       </c>
       <c r="E30" t="n">
-        <v>621.9797516577522</v>
+        <v>621.9796906937136</v>
       </c>
       <c r="F30" t="n">
-        <v>634.652728054257</v>
+        <v>634.6526658480624</v>
       </c>
       <c r="G30" t="n">
         <v>8951100</v>
@@ -1300,16 +1300,16 @@
         <v>46078</v>
       </c>
       <c r="C38" t="n">
-        <v>633.6785888671875</v>
+        <v>633.6786499023438</v>
       </c>
       <c r="D38" t="n">
-        <v>634.1457203877115</v>
+        <v>634.1457814678613</v>
       </c>
       <c r="E38" t="n">
-        <v>630.9054049624871</v>
+        <v>630.9054657305335</v>
       </c>
       <c r="F38" t="n">
-        <v>630.9352528466555</v>
+        <v>630.935313617577</v>
       </c>
       <c r="G38" t="n">
         <v>12135200</v>
@@ -1346,16 +1346,16 @@
         <v>46080</v>
       </c>
       <c r="C40" t="n">
-        <v>627.227783203125</v>
+        <v>627.2277221679688</v>
       </c>
       <c r="D40" t="n">
-        <v>627.8738807349088</v>
+        <v>627.8738196368811</v>
       </c>
       <c r="E40" t="n">
-        <v>623.1525761045295</v>
+        <v>623.1525154659292</v>
       </c>
       <c r="F40" t="n">
-        <v>624.4447105016621</v>
+        <v>624.444649737325</v>
       </c>
       <c r="G40" t="n">
         <v>10471100</v>
@@ -1438,16 +1438,16 @@
         <v>46086</v>
       </c>
       <c r="C44" t="n">
-        <v>623.0233154296875</v>
+        <v>623.0233764648438</v>
       </c>
       <c r="D44" t="n">
-        <v>626.6910258426402</v>
+        <v>626.6910872371077</v>
       </c>
       <c r="E44" t="n">
-        <v>617.646024993958</v>
+        <v>617.6460855023222</v>
       </c>
       <c r="F44" t="n">
-        <v>623.5003962422892</v>
+        <v>623.5004573241831</v>
       </c>
       <c r="G44" t="n">
         <v>12198800</v>
@@ -1484,16 +1484,16 @@
         <v>46090</v>
       </c>
       <c r="C46" t="n">
-        <v>620.031494140625</v>
+        <v>620.0315551757812</v>
       </c>
       <c r="D46" t="n">
-        <v>621.542330946535</v>
+        <v>621.5423921304164</v>
       </c>
       <c r="E46" t="n">
-        <v>605.5197197672502</v>
+        <v>605.5197793738849</v>
       </c>
       <c r="F46" t="n">
-        <v>609.1575823221168</v>
+        <v>609.1576422868583</v>
       </c>
       <c r="G46" t="n">
         <v>13929200</v>
@@ -1530,16 +1530,16 @@
         <v>46092</v>
       </c>
       <c r="C48" t="n">
-        <v>618.272216796875</v>
+        <v>618.2722778320312</v>
       </c>
       <c r="D48" t="n">
-        <v>621.6516402913978</v>
+        <v>621.651701660167</v>
       </c>
       <c r="E48" t="n">
-        <v>615.5586680402731</v>
+        <v>615.5587288075508</v>
       </c>
       <c r="F48" t="n">
-        <v>619.4351315974586</v>
+        <v>619.4351927474164</v>
       </c>
       <c r="G48" t="n">
         <v>6433300</v>
@@ -1553,16 +1553,16 @@
         <v>46093</v>
       </c>
       <c r="C49" t="n">
-        <v>608.7998046875</v>
+        <v>608.7997436523438</v>
       </c>
       <c r="D49" t="n">
-        <v>613.9783522130032</v>
+        <v>613.9782906586722</v>
       </c>
       <c r="E49" t="n">
-        <v>608.7202709917146</v>
+        <v>608.720209964532</v>
       </c>
       <c r="F49" t="n">
-        <v>613.491261409448</v>
+        <v>613.4911999039504</v>
       </c>
       <c r="G49" t="n">
         <v>15487600</v>
@@ -1599,16 +1599,16 @@
         <v>46097</v>
       </c>
       <c r="C51" t="n">
-        <v>611.4735717773438</v>
+        <v>611.4735107421875</v>
       </c>
       <c r="D51" t="n">
-        <v>614.3461275285033</v>
+        <v>614.3460662066185</v>
       </c>
       <c r="E51" t="n">
-        <v>609.8335153427746</v>
+        <v>609.8334544713231</v>
       </c>
       <c r="F51" t="n">
-        <v>611.006379552641</v>
+        <v>611.0063185641181</v>
       </c>
       <c r="G51" t="n">
         <v>8303200</v>
@@ -1622,16 +1622,16 @@
         <v>46098</v>
       </c>
       <c r="C52" t="n">
-        <v>613.1632690429688</v>
+        <v>613.163330078125</v>
       </c>
       <c r="D52" t="n">
-        <v>616.5228546969976</v>
+        <v>616.5229160665718</v>
       </c>
       <c r="E52" t="n">
-        <v>612.5470194298802</v>
+        <v>612.5470804036939</v>
       </c>
       <c r="F52" t="n">
-        <v>614.6343086785441</v>
+        <v>614.6343698601297</v>
       </c>
       <c r="G52" t="n">
         <v>9941800</v>
@@ -1714,16 +1714,16 @@
         <v>46104</v>
       </c>
       <c r="C56" t="n">
-        <v>600.778564453125</v>
+        <v>600.7785034179688</v>
       </c>
       <c r="D56" t="n">
-        <v>607.3387295253531</v>
+        <v>607.3386678237272</v>
       </c>
       <c r="E56" t="n">
-        <v>599.416845627479</v>
+        <v>599.4167847306644</v>
       </c>
       <c r="F56" t="n">
-        <v>603.1938772752512</v>
+        <v>603.193815994715</v>
       </c>
       <c r="G56" t="n">
         <v>24014300</v>
@@ -1737,16 +1737,16 @@
         <v>46105</v>
       </c>
       <c r="C57" t="n">
-        <v>598.7409057617188</v>
+        <v>598.740966796875</v>
       </c>
       <c r="D57" t="n">
-        <v>602.2495487731062</v>
+        <v>602.2496101659307</v>
       </c>
       <c r="E57" t="n">
-        <v>595.6993942656367</v>
+        <v>595.6994549907438</v>
       </c>
       <c r="F57" t="n">
-        <v>597.0014778647273</v>
+        <v>597.0015387225677</v>
       </c>
       <c r="G57" t="n">
         <v>18363300</v>
@@ -1760,16 +1760,16 @@
         <v>46106</v>
       </c>
       <c r="C58" t="n">
-        <v>602.0010375976562</v>
+        <v>602.0010986328125</v>
       </c>
       <c r="D58" t="n">
-        <v>605.7582308410098</v>
+        <v>605.7582922570971</v>
       </c>
       <c r="E58" t="n">
-        <v>599.7149445764509</v>
+        <v>599.7150053798267</v>
       </c>
       <c r="F58" t="n">
-        <v>603.7305768047668</v>
+        <v>603.730638015276</v>
       </c>
       <c r="G58" t="n">
         <v>23288300</v>
@@ -3879,7 +3879,7 @@
         <v>706.4000244140625</v>
       </c>
       <c r="D150" t="n">
-        <v>709.4619140625</v>
+        <v>709.4600219726562</v>
       </c>
       <c r="E150" t="n">
         <v>705.4299926757812</v>
@@ -3888,7 +3888,145 @@
         <v>707.9299926757812</v>
       </c>
       <c r="G150" t="n">
-        <v>4302202</v>
+        <v>4668700</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C151" t="n">
+        <v>710.7100219726562</v>
+      </c>
+      <c r="D151" t="n">
+        <v>711.3699951171875</v>
+      </c>
+      <c r="E151" t="n">
+        <v>707.4400024414062</v>
+      </c>
+      <c r="F151" t="n">
+        <v>708.72998046875</v>
+      </c>
+      <c r="G151" t="n">
+        <v>4653100</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C152" t="n">
+        <v>710.6500244140625</v>
+      </c>
+      <c r="D152" t="n">
+        <v>712.4400024414062</v>
+      </c>
+      <c r="E152" t="n">
+        <v>709.5</v>
+      </c>
+      <c r="F152" t="n">
+        <v>710.3099975585938</v>
+      </c>
+      <c r="G152" t="n">
+        <v>6689300</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C153" t="n">
+        <v>708.4199829101562</v>
+      </c>
+      <c r="D153" t="n">
+        <v>712</v>
+      </c>
+      <c r="E153" t="n">
+        <v>707</v>
+      </c>
+      <c r="F153" t="n">
+        <v>711.9600219726562</v>
+      </c>
+      <c r="G153" t="n">
+        <v>5169300</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C154" t="n">
+        <v>710.1699829101562</v>
+      </c>
+      <c r="D154" t="n">
+        <v>712.260009765625</v>
+      </c>
+      <c r="E154" t="n">
+        <v>708.9299926757812</v>
+      </c>
+      <c r="F154" t="n">
+        <v>712.1199951171875</v>
+      </c>
+      <c r="G154" t="n">
+        <v>4919100</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C155" t="n">
+        <v>714.9500122070312</v>
+      </c>
+      <c r="D155" t="n">
+        <v>716.3900146484375</v>
+      </c>
+      <c r="E155" t="n">
+        <v>711.6099853515625</v>
+      </c>
+      <c r="F155" t="n">
+        <v>712.2999877929688</v>
+      </c>
+      <c r="G155" t="n">
+        <v>4590000</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="C156" t="n">
+        <v>713.6099853515625</v>
+      </c>
+      <c r="D156" t="n">
+        <v>715.8900146484375</v>
+      </c>
+      <c r="E156" t="n">
+        <v>712.7999877929688</v>
+      </c>
+      <c r="F156" t="n">
+        <v>715.6300048828125</v>
+      </c>
+      <c r="G156" t="n">
+        <v>4148693</v>
       </c>
     </row>
   </sheetData>

--- a/Data/voo.xlsx
+++ b/Data/voo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4026,7 +4026,53 @@
         <v>715.6300048828125</v>
       </c>
       <c r="G156" t="n">
-        <v>4148693</v>
+        <v>4236400</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C157" t="n">
+        <v>710.27001953125</v>
+      </c>
+      <c r="D157" t="n">
+        <v>714.0499877929688</v>
+      </c>
+      <c r="E157" t="n">
+        <v>710.0999755859375</v>
+      </c>
+      <c r="F157" t="n">
+        <v>713.5</v>
+      </c>
+      <c r="G157" t="n">
+        <v>5745000</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C158" t="n">
+        <v>705.4000244140625</v>
+      </c>
+      <c r="D158" t="n">
+        <v>707.3499755859375</v>
+      </c>
+      <c r="E158" t="n">
+        <v>704.989990234375</v>
+      </c>
+      <c r="F158" t="n">
+        <v>706.6099853515625</v>
+      </c>
+      <c r="G158" t="n">
+        <v>4379375</v>
       </c>
     </row>
   </sheetData>

--- a/Data/voo.xlsx
+++ b/Data/voo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G158"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4066,13 +4066,36 @@
         <v>707.3499755859375</v>
       </c>
       <c r="E158" t="n">
-        <v>704.989990234375</v>
+        <v>704.9600219726562</v>
       </c>
       <c r="F158" t="n">
         <v>706.6099853515625</v>
       </c>
       <c r="G158" t="n">
-        <v>4379375</v>
+        <v>5278600</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C159" t="n">
+        <v>707.14501953125</v>
+      </c>
+      <c r="D159" t="n">
+        <v>710.0850219726562</v>
+      </c>
+      <c r="E159" t="n">
+        <v>706.094970703125</v>
+      </c>
+      <c r="F159" t="n">
+        <v>708.1900024414062</v>
+      </c>
+      <c r="G159" t="n">
+        <v>3820489</v>
       </c>
     </row>
   </sheetData>

--- a/Data/voo.xlsx
+++ b/Data/voo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,16 +495,16 @@
         <v>46027</v>
       </c>
       <c r="C3" t="n">
-        <v>628.6392211914062</v>
+        <v>628.6392822265625</v>
       </c>
       <c r="D3" t="n">
-        <v>630.2096324573033</v>
+        <v>630.2096936449323</v>
       </c>
       <c r="E3" t="n">
-        <v>627.4166105817476</v>
+        <v>627.4166714981994</v>
       </c>
       <c r="F3" t="n">
-        <v>627.565728672282</v>
+        <v>627.5657896032119</v>
       </c>
       <c r="G3" t="n">
         <v>16175600</v>
@@ -541,16 +541,16 @@
         <v>46029</v>
       </c>
       <c r="C5" t="n">
-        <v>630.3388061523438</v>
+        <v>630.3388671875</v>
       </c>
       <c r="D5" t="n">
-        <v>634.3643269734911</v>
+        <v>634.364388398435</v>
       </c>
       <c r="E5" t="n">
-        <v>630.1002657579688</v>
+        <v>630.1003267700273</v>
       </c>
       <c r="F5" t="n">
-        <v>632.7342807231195</v>
+        <v>632.7343419902274</v>
       </c>
       <c r="G5" t="n">
         <v>8820100</v>
@@ -587,16 +587,16 @@
         <v>46031</v>
       </c>
       <c r="C7" t="n">
-        <v>634.4539184570312</v>
+        <v>634.453857421875</v>
       </c>
       <c r="D7" t="n">
-        <v>635.5770968946526</v>
+        <v>635.5770357514454</v>
       </c>
       <c r="E7" t="n">
-        <v>629.9711540024175</v>
+        <v>629.9710933985081</v>
       </c>
       <c r="F7" t="n">
-        <v>631.313034949903</v>
+        <v>631.3129742169032</v>
       </c>
       <c r="G7" t="n">
         <v>7864100</v>
@@ -610,16 +610,16 @@
         <v>46034</v>
       </c>
       <c r="C8" t="n">
-        <v>635.4777221679688</v>
+        <v>635.4776611328125</v>
       </c>
       <c r="D8" t="n">
-        <v>636.2927150953415</v>
+        <v>636.2926539819083</v>
       </c>
       <c r="E8" t="n">
-        <v>631.3229204987674</v>
+        <v>631.3228598626637</v>
       </c>
       <c r="F8" t="n">
-        <v>631.3527683862371</v>
+        <v>631.3527077472665</v>
       </c>
       <c r="G8" t="n">
         <v>7929800</v>
@@ -679,16 +679,16 @@
         <v>46037</v>
       </c>
       <c r="C11" t="n">
-        <v>632.7741088867188</v>
+        <v>632.7740478515625</v>
       </c>
       <c r="D11" t="n">
-        <v>635.716249065159</v>
+        <v>635.7161877462142</v>
       </c>
       <c r="E11" t="n">
-        <v>631.8596836870233</v>
+        <v>631.8596227400693</v>
       </c>
       <c r="F11" t="n">
-        <v>634.9111447843152</v>
+        <v>634.911083543028</v>
       </c>
       <c r="G11" t="n">
         <v>6937000</v>
@@ -863,16 +863,16 @@
         <v>46050</v>
       </c>
       <c r="C19" t="n">
-        <v>635.7360229492188</v>
+        <v>635.736083984375</v>
       </c>
       <c r="D19" t="n">
-        <v>637.9326937327655</v>
+        <v>637.9327549788177</v>
       </c>
       <c r="E19" t="n">
-        <v>634.3643549546319</v>
+        <v>634.3644158580984</v>
       </c>
       <c r="F19" t="n">
-        <v>637.1772753396389</v>
+        <v>637.1773365131655</v>
       </c>
       <c r="G19" t="n">
         <v>5568700</v>
@@ -1001,16 +1001,16 @@
         <v>46058</v>
       </c>
       <c r="C25" t="n">
-        <v>619.3357543945312</v>
+        <v>619.335693359375</v>
       </c>
       <c r="D25" t="n">
-        <v>624.9516463379395</v>
+        <v>624.9515847493406</v>
       </c>
       <c r="E25" t="n">
-        <v>617.7454444517366</v>
+        <v>617.7453835733044</v>
       </c>
       <c r="F25" t="n">
-        <v>622.4567998403622</v>
+        <v>622.456738497629</v>
       </c>
       <c r="G25" t="n">
         <v>11714700</v>
@@ -1070,16 +1070,16 @@
         <v>46063</v>
       </c>
       <c r="C28" t="n">
-        <v>632.5951538085938</v>
+        <v>632.59521484375</v>
       </c>
       <c r="D28" t="n">
-        <v>636.7498943960981</v>
+        <v>636.7499558321192</v>
       </c>
       <c r="E28" t="n">
-        <v>632.237343193348</v>
+        <v>632.2374041939814</v>
       </c>
       <c r="F28" t="n">
-        <v>635.2788547558001</v>
+        <v>635.2789160498899</v>
       </c>
       <c r="G28" t="n">
         <v>13645300</v>
@@ -1116,16 +1116,16 @@
         <v>46065</v>
       </c>
       <c r="C30" t="n">
-        <v>622.7052612304688</v>
+        <v>622.705322265625</v>
       </c>
       <c r="D30" t="n">
-        <v>635.6565739786832</v>
+        <v>635.656636283277</v>
       </c>
       <c r="E30" t="n">
-        <v>621.9796906937136</v>
+        <v>621.9797516577522</v>
       </c>
       <c r="F30" t="n">
-        <v>634.6526658480624</v>
+        <v>634.652728054257</v>
       </c>
       <c r="G30" t="n">
         <v>8951100</v>
@@ -1300,16 +1300,16 @@
         <v>46078</v>
       </c>
       <c r="C38" t="n">
-        <v>633.6786499023438</v>
+        <v>633.6785888671875</v>
       </c>
       <c r="D38" t="n">
-        <v>634.1457814678613</v>
+        <v>634.1457203877115</v>
       </c>
       <c r="E38" t="n">
-        <v>630.9054657305335</v>
+        <v>630.9054049624871</v>
       </c>
       <c r="F38" t="n">
-        <v>630.935313617577</v>
+        <v>630.9352528466555</v>
       </c>
       <c r="G38" t="n">
         <v>12135200</v>
@@ -1346,16 +1346,16 @@
         <v>46080</v>
       </c>
       <c r="C40" t="n">
-        <v>627.2277221679688</v>
+        <v>627.227783203125</v>
       </c>
       <c r="D40" t="n">
-        <v>627.8738196368811</v>
+        <v>627.8738807349088</v>
       </c>
       <c r="E40" t="n">
-        <v>623.1525154659292</v>
+        <v>623.1525761045295</v>
       </c>
       <c r="F40" t="n">
-        <v>624.444649737325</v>
+        <v>624.4447105016621</v>
       </c>
       <c r="G40" t="n">
         <v>10471100</v>
@@ -1438,16 +1438,16 @@
         <v>46086</v>
       </c>
       <c r="C44" t="n">
-        <v>623.0233764648438</v>
+        <v>623.0233154296875</v>
       </c>
       <c r="D44" t="n">
-        <v>626.6910872371077</v>
+        <v>626.6910258426402</v>
       </c>
       <c r="E44" t="n">
-        <v>617.6460855023222</v>
+        <v>617.646024993958</v>
       </c>
       <c r="F44" t="n">
-        <v>623.5004573241831</v>
+        <v>623.5003962422892</v>
       </c>
       <c r="G44" t="n">
         <v>12198800</v>
@@ -1484,16 +1484,16 @@
         <v>46090</v>
       </c>
       <c r="C46" t="n">
-        <v>620.0315551757812</v>
+        <v>620.031494140625</v>
       </c>
       <c r="D46" t="n">
-        <v>621.5423921304164</v>
+        <v>621.542330946535</v>
       </c>
       <c r="E46" t="n">
-        <v>605.5197793738849</v>
+        <v>605.5197197672502</v>
       </c>
       <c r="F46" t="n">
-        <v>609.1576422868583</v>
+        <v>609.1575823221168</v>
       </c>
       <c r="G46" t="n">
         <v>13929200</v>
@@ -1530,16 +1530,16 @@
         <v>46092</v>
       </c>
       <c r="C48" t="n">
-        <v>618.2722778320312</v>
+        <v>618.272216796875</v>
       </c>
       <c r="D48" t="n">
-        <v>621.651701660167</v>
+        <v>621.6516402913978</v>
       </c>
       <c r="E48" t="n">
-        <v>615.5587288075508</v>
+        <v>615.5586680402731</v>
       </c>
       <c r="F48" t="n">
-        <v>619.4351927474164</v>
+        <v>619.4351315974586</v>
       </c>
       <c r="G48" t="n">
         <v>6433300</v>
@@ -1553,16 +1553,16 @@
         <v>46093</v>
       </c>
       <c r="C49" t="n">
-        <v>608.7997436523438</v>
+        <v>608.7998046875</v>
       </c>
       <c r="D49" t="n">
-        <v>613.9782906586722</v>
+        <v>613.9783522130032</v>
       </c>
       <c r="E49" t="n">
-        <v>608.720209964532</v>
+        <v>608.7202709917146</v>
       </c>
       <c r="F49" t="n">
-        <v>613.4911999039504</v>
+        <v>613.491261409448</v>
       </c>
       <c r="G49" t="n">
         <v>15487600</v>
@@ -1599,16 +1599,16 @@
         <v>46097</v>
       </c>
       <c r="C51" t="n">
-        <v>611.4735107421875</v>
+        <v>611.4735717773438</v>
       </c>
       <c r="D51" t="n">
-        <v>614.3460662066185</v>
+        <v>614.3461275285033</v>
       </c>
       <c r="E51" t="n">
-        <v>609.8334544713231</v>
+        <v>609.8335153427746</v>
       </c>
       <c r="F51" t="n">
-        <v>611.0063185641181</v>
+        <v>611.006379552641</v>
       </c>
       <c r="G51" t="n">
         <v>8303200</v>
@@ -1622,16 +1622,16 @@
         <v>46098</v>
       </c>
       <c r="C52" t="n">
-        <v>613.163330078125</v>
+        <v>613.1632690429688</v>
       </c>
       <c r="D52" t="n">
-        <v>616.5229160665718</v>
+        <v>616.5228546969976</v>
       </c>
       <c r="E52" t="n">
-        <v>612.5470804036939</v>
+        <v>612.5470194298802</v>
       </c>
       <c r="F52" t="n">
-        <v>614.6343698601297</v>
+        <v>614.6343086785441</v>
       </c>
       <c r="G52" t="n">
         <v>9941800</v>
@@ -1714,16 +1714,16 @@
         <v>46104</v>
       </c>
       <c r="C56" t="n">
-        <v>600.7785034179688</v>
+        <v>600.778564453125</v>
       </c>
       <c r="D56" t="n">
-        <v>607.3386678237272</v>
+        <v>607.3387295253531</v>
       </c>
       <c r="E56" t="n">
-        <v>599.4167847306644</v>
+        <v>599.416845627479</v>
       </c>
       <c r="F56" t="n">
-        <v>603.193815994715</v>
+        <v>603.1938772752512</v>
       </c>
       <c r="G56" t="n">
         <v>24014300</v>
@@ -1737,16 +1737,16 @@
         <v>46105</v>
       </c>
       <c r="C57" t="n">
-        <v>598.740966796875</v>
+        <v>598.7409057617188</v>
       </c>
       <c r="D57" t="n">
-        <v>602.2496101659307</v>
+        <v>602.2495487731062</v>
       </c>
       <c r="E57" t="n">
-        <v>595.6994549907438</v>
+        <v>595.6993942656367</v>
       </c>
       <c r="F57" t="n">
-        <v>597.0015387225677</v>
+        <v>597.0014778647273</v>
       </c>
       <c r="G57" t="n">
         <v>18363300</v>
@@ -1760,16 +1760,16 @@
         <v>46106</v>
       </c>
       <c r="C58" t="n">
-        <v>602.0010986328125</v>
+        <v>602.0010375976562</v>
       </c>
       <c r="D58" t="n">
-        <v>605.7582922570971</v>
+        <v>605.7582308410098</v>
       </c>
       <c r="E58" t="n">
-        <v>599.7150053798267</v>
+        <v>599.7149445764509</v>
       </c>
       <c r="F58" t="n">
-        <v>603.730638015276</v>
+        <v>603.7305768047668</v>
       </c>
       <c r="G58" t="n">
         <v>23288300</v>
@@ -4083,19 +4083,157 @@
         <v>46253</v>
       </c>
       <c r="C159" t="n">
-        <v>707.14501953125</v>
+        <v>706.9099731445312</v>
       </c>
       <c r="D159" t="n">
-        <v>710.0850219726562</v>
+        <v>710.0999755859375</v>
       </c>
       <c r="E159" t="n">
-        <v>706.094970703125</v>
+        <v>706.0999755859375</v>
       </c>
       <c r="F159" t="n">
         <v>708.1900024414062</v>
       </c>
       <c r="G159" t="n">
-        <v>3820489</v>
+        <v>7021800</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C160" t="n">
+        <v>701.010009765625</v>
+      </c>
+      <c r="D160" t="n">
+        <v>706.0800170898438</v>
+      </c>
+      <c r="E160" t="n">
+        <v>700.469970703125</v>
+      </c>
+      <c r="F160" t="n">
+        <v>704.0499877929688</v>
+      </c>
+      <c r="G160" t="n">
+        <v>8458600</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C161" t="n">
+        <v>703.7100219726562</v>
+      </c>
+      <c r="D161" t="n">
+        <v>705.7999877929688</v>
+      </c>
+      <c r="E161" t="n">
+        <v>702.4400024414062</v>
+      </c>
+      <c r="F161" t="n">
+        <v>704.0700073242188</v>
+      </c>
+      <c r="G161" t="n">
+        <v>10712800</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C162" t="n">
+        <v>701.8300170898438</v>
+      </c>
+      <c r="D162" t="n">
+        <v>703.3900146484375</v>
+      </c>
+      <c r="E162" t="n">
+        <v>700.530029296875</v>
+      </c>
+      <c r="F162" t="n">
+        <v>702.969970703125</v>
+      </c>
+      <c r="G162" t="n">
+        <v>7727600</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C163" t="n">
+        <v>704.02001953125</v>
+      </c>
+      <c r="D163" t="n">
+        <v>704.8400268554688</v>
+      </c>
+      <c r="E163" t="n">
+        <v>701.4500122070312</v>
+      </c>
+      <c r="F163" t="n">
+        <v>704.2899780273438</v>
+      </c>
+      <c r="G163" t="n">
+        <v>4315600</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C164" t="n">
+        <v>704.2000122070312</v>
+      </c>
+      <c r="D164" t="n">
+        <v>705.3200073242188</v>
+      </c>
+      <c r="E164" t="n">
+        <v>702.22998046875</v>
+      </c>
+      <c r="F164" t="n">
+        <v>702.9000244140625</v>
+      </c>
+      <c r="G164" t="n">
+        <v>7157800</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" s="2" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C165" t="n">
+        <v>708.75</v>
+      </c>
+      <c r="D165" t="n">
+        <v>709.9550170898438</v>
+      </c>
+      <c r="E165" t="n">
+        <v>705.2103881835938</v>
+      </c>
+      <c r="F165" t="n">
+        <v>706.3900146484375</v>
+      </c>
+      <c r="G165" t="n">
+        <v>6737734</v>
       </c>
     </row>
   </sheetData>

--- a/Data/voo.xlsx
+++ b/Data/voo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4224,16 +4224,85 @@
         <v>708.75</v>
       </c>
       <c r="D165" t="n">
-        <v>709.9550170898438</v>
+        <v>709.9600219726562</v>
       </c>
       <c r="E165" t="n">
-        <v>705.2103881835938</v>
+        <v>705.2100219726562</v>
       </c>
       <c r="F165" t="n">
         <v>706.3900146484375</v>
       </c>
       <c r="G165" t="n">
-        <v>6737734</v>
+        <v>6745700</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C166" t="n">
+        <v>707.239990234375</v>
+      </c>
+      <c r="D166" t="n">
+        <v>712.6699829101562</v>
+      </c>
+      <c r="E166" t="n">
+        <v>706.260009765625</v>
+      </c>
+      <c r="F166" t="n">
+        <v>709.3900146484375</v>
+      </c>
+      <c r="G166" t="n">
+        <v>8084500</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C167" t="n">
+        <v>704.8900146484375</v>
+      </c>
+      <c r="D167" t="n">
+        <v>705.9400024414062</v>
+      </c>
+      <c r="E167" t="n">
+        <v>702.9600219726562</v>
+      </c>
+      <c r="F167" t="n">
+        <v>705.3599853515625</v>
+      </c>
+      <c r="G167" t="n">
+        <v>5733400</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C168" t="n">
+        <v>700.280029296875</v>
+      </c>
+      <c r="D168" t="n">
+        <v>702.9099731445312</v>
+      </c>
+      <c r="E168" t="n">
+        <v>698.1397705078125</v>
+      </c>
+      <c r="F168" t="n">
+        <v>700.4500122070312</v>
+      </c>
+      <c r="G168" t="n">
+        <v>6464469</v>
       </c>
     </row>
   </sheetData>
